--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -67,66 +67,69 @@
     <t>نام محصول</t>
   </si>
   <si>
+    <t>برند</t>
+  </si>
+  <si>
+    <t>کد محصول</t>
+  </si>
+  <si>
     <t>راهنما</t>
   </si>
   <si>
+    <t>قیمت نقد</t>
+  </si>
+  <si>
     <t>نمایش محصول</t>
   </si>
   <si>
-    <t>برند</t>
+    <t>دسته‌بندی</t>
+  </si>
+  <si>
+    <t>توضیحات</t>
   </si>
   <si>
     <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
   </si>
   <si>
-    <t>کد محصول</t>
-  </si>
-  <si>
     <t>موجود کردن</t>
   </si>
   <si>
+    <t>عکس</t>
+  </si>
+  <si>
     <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
   </si>
   <si>
-    <t>قیمت نقد</t>
+    <t>دسته‌بندی اصلی</t>
   </si>
   <si>
     <t>ناموجود کردن</t>
   </si>
   <si>
+    <t>گروه اصلی</t>
+  </si>
+  <si>
     <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
   </si>
   <si>
     <t>فهرست برندها</t>
   </si>
   <si>
-    <t>دسته‌بندی</t>
-  </si>
-  <si>
     <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
   </si>
   <si>
+    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
+  </si>
+  <si>
     <t>عکس محصول</t>
   </si>
   <si>
-    <t>توضیحات</t>
-  </si>
-  <si>
     <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
   </si>
   <si>
-    <t>عکس</t>
-  </si>
-  <si>
-    <t>دسته‌بندی اصلی</t>
-  </si>
-  <si>
     <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
   </si>
   <si>
-    <t>گروه اصلی</t>
-  </si>
-  <si>
     <t>آرایشی و بهداشتی</t>
   </si>
   <si>
@@ -136,9 +139,6 @@
     <t>دسته‌بندی‌های مجاز</t>
   </si>
   <si>
-    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
-  </si>
-  <si>
     <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
   </si>
   <si>
@@ -148,13 +148,13 @@
     <t>Product</t>
   </si>
   <si>
+    <t>پوشه بنرها</t>
+  </si>
+  <si>
+    <t>baner</t>
+  </si>
+  <si>
     <t>اپل</t>
-  </si>
-  <si>
-    <t>پوشه بنرها</t>
-  </si>
-  <si>
-    <t>baner</t>
   </si>
   <si>
     <t>1109410629</t>
@@ -7758,16 +7758,16 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -8044,40 +8044,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>21</v>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>32</v>
@@ -8102,7 +8102,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>36</v>
@@ -8129,7 +8129,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>39</v>
@@ -8154,7 +8154,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>42</v>
@@ -8177,7 +8177,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>44</v>
@@ -8204,7 +8204,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>48</v>
@@ -8231,7 +8231,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>50</v>
@@ -8258,7 +8258,7 @@
         <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>52</v>
@@ -8285,7 +8285,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>54</v>
@@ -8312,7 +8312,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>56</v>
@@ -8337,7 +8337,7 @@
         <v>57</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>58</v>
@@ -8360,7 +8360,7 @@
         <v>59</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>60</v>
@@ -8385,7 +8385,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>62</v>
@@ -8408,7 +8408,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>64</v>
@@ -8431,7 +8431,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>66</v>
@@ -8456,7 +8456,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>68</v>
@@ -8479,7 +8479,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>70</v>
@@ -8504,7 +8504,7 @@
         <v>71</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>72</v>
@@ -8527,7 +8527,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>74</v>
@@ -8550,7 +8550,7 @@
         <v>75</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>76</v>
@@ -8573,7 +8573,7 @@
         <v>77</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>78</v>
@@ -8596,7 +8596,7 @@
         <v>79</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>80</v>
@@ -8619,7 +8619,7 @@
         <v>81</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>82</v>
@@ -8642,7 +8642,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>84</v>
@@ -8665,7 +8665,7 @@
         <v>85</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>86</v>
@@ -8688,7 +8688,7 @@
         <v>87</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>88</v>
@@ -8711,7 +8711,7 @@
         <v>89</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>90</v>
@@ -8734,7 +8734,7 @@
         <v>91</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>92</v>
@@ -8757,7 +8757,7 @@
         <v>93</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>94</v>
@@ -8780,7 +8780,7 @@
         <v>95</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>96</v>
@@ -8803,7 +8803,7 @@
         <v>97</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>98</v>
@@ -8826,7 +8826,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>100</v>
@@ -8849,7 +8849,7 @@
         <v>101</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>102</v>
@@ -8872,7 +8872,7 @@
         <v>103</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>104</v>
@@ -8895,7 +8895,7 @@
         <v>105</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>106</v>
@@ -8918,7 +8918,7 @@
         <v>107</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>108</v>
@@ -8941,7 +8941,7 @@
         <v>109</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>110</v>
@@ -8964,7 +8964,7 @@
         <v>111</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>112</v>
@@ -8987,7 +8987,7 @@
         <v>113</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>114</v>
@@ -9010,7 +9010,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>116</v>
@@ -9033,7 +9033,7 @@
         <v>117</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>118</v>
@@ -9056,7 +9056,7 @@
         <v>119</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>120</v>
@@ -9079,7 +9079,7 @@
         <v>121</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>122</v>
@@ -9102,7 +9102,7 @@
         <v>123</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>124</v>
@@ -9125,7 +9125,7 @@
         <v>125</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>126</v>
@@ -9148,7 +9148,7 @@
         <v>127</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>128</v>
@@ -9171,7 +9171,7 @@
         <v>129</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>130</v>
@@ -9194,7 +9194,7 @@
         <v>131</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>132</v>
@@ -9217,7 +9217,7 @@
         <v>133</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>134</v>
@@ -9240,7 +9240,7 @@
         <v>135</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>136</v>
@@ -9263,7 +9263,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>138</v>
@@ -9286,7 +9286,7 @@
         <v>139</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>140</v>
@@ -9309,7 +9309,7 @@
         <v>141</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>142</v>
@@ -9332,7 +9332,7 @@
         <v>143</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>144</v>
@@ -9355,7 +9355,7 @@
         <v>145</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>146</v>
@@ -9378,7 +9378,7 @@
         <v>147</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>148</v>
@@ -9403,7 +9403,7 @@
         <v>149</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>150</v>
@@ -9428,7 +9428,7 @@
         <v>151</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>152</v>
@@ -9453,7 +9453,7 @@
         <v>153</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>154</v>
@@ -9478,7 +9478,7 @@
         <v>155</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>156</v>
@@ -9503,7 +9503,7 @@
         <v>157</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>158</v>
@@ -9528,7 +9528,7 @@
         <v>159</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>160</v>
@@ -9553,7 +9553,7 @@
         <v>161</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>162</v>
@@ -9578,7 +9578,7 @@
         <v>163</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>164</v>
@@ -9603,7 +9603,7 @@
         <v>165</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>166</v>
@@ -9626,7 +9626,7 @@
         <v>169</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>170</v>
@@ -9649,7 +9649,7 @@
         <v>171</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>172</v>
@@ -9674,7 +9674,7 @@
         <v>174</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>175</v>
@@ -9699,7 +9699,7 @@
         <v>174</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>178</v>
@@ -9724,7 +9724,7 @@
         <v>179</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>180</v>
@@ -9749,7 +9749,7 @@
         <v>182</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>183</v>
@@ -9772,7 +9772,7 @@
         <v>184</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>185</v>
@@ -9797,7 +9797,7 @@
         <v>174</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>186</v>
@@ -9822,7 +9822,7 @@
         <v>187</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>188</v>
@@ -9847,7 +9847,7 @@
         <v>189</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>190</v>
@@ -18839,9 +18839,7 @@
       <c r="C463" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="D463" s="11">
-        <v>3389000.0</v>
-      </c>
+      <c r="D463" s="11"/>
       <c r="E463" s="6" t="s">
         <v>33</v>
       </c>
@@ -18868,9 +18866,7 @@
       <c r="C464" s="7" t="s">
         <v>987</v>
       </c>
-      <c r="D464" s="11">
-        <v>3163000.0</v>
-      </c>
+      <c r="D464" s="11"/>
       <c r="E464" s="6" t="s">
         <v>33</v>
       </c>
@@ -18897,9 +18893,7 @@
       <c r="C465" s="7" t="s">
         <v>990</v>
       </c>
-      <c r="D465" s="11">
-        <v>7853000.0</v>
-      </c>
+      <c r="D465" s="11"/>
       <c r="E465" s="6" t="s">
         <v>33</v>
       </c>
@@ -18926,9 +18920,7 @@
       <c r="C466" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="D466" s="11">
-        <v>4327000.0</v>
-      </c>
+      <c r="D466" s="11"/>
       <c r="E466" s="6" t="s">
         <v>33</v>
       </c>
@@ -24181,9 +24173,7 @@
       <c r="C693" s="7" t="s">
         <v>1488</v>
       </c>
-      <c r="D693" s="11">
-        <v>3613000.0</v>
-      </c>
+      <c r="D693" s="11"/>
       <c r="E693" s="6" t="s">
         <v>33</v>
       </c>
@@ -24210,9 +24200,7 @@
       <c r="C694" s="7" t="s">
         <v>1492</v>
       </c>
-      <c r="D694" s="11">
-        <v>3613000.0</v>
-      </c>
+      <c r="D694" s="11"/>
       <c r="E694" s="6" t="s">
         <v>33</v>
       </c>
@@ -24408,9 +24396,7 @@
       <c r="C702" s="7" t="s">
         <v>1509</v>
       </c>
-      <c r="D702" s="11">
-        <v>5921000.0</v>
-      </c>
+      <c r="D702" s="11"/>
       <c r="E702" s="6" t="s">
         <v>33</v>
       </c>
@@ -24437,9 +24423,7 @@
       <c r="C703" s="7" t="s">
         <v>1512</v>
       </c>
-      <c r="D703" s="11">
-        <v>4406000.0</v>
-      </c>
+      <c r="D703" s="11"/>
       <c r="E703" s="6" t="s">
         <v>33</v>
       </c>
@@ -24466,9 +24450,7 @@
       <c r="C704" s="7" t="s">
         <v>1515</v>
       </c>
-      <c r="D704" s="11">
-        <v>3898000.0</v>
-      </c>
+      <c r="D704" s="11"/>
       <c r="E704" s="6" t="s">
         <v>33</v>
       </c>
@@ -24659,14 +24641,12 @@
         <v>1532</v>
       </c>
       <c r="B712" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C712" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="D712" s="11">
-        <v>4.52E7</v>
-      </c>
+      <c r="D712" s="11"/>
       <c r="E712" s="6" t="s">
         <v>167</v>
       </c>
@@ -24688,14 +24668,12 @@
         <v>1536</v>
       </c>
       <c r="B713" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C713" s="7" t="s">
         <v>1537</v>
       </c>
-      <c r="D713" s="11">
-        <v>3.729E7</v>
-      </c>
+      <c r="D713" s="11"/>
       <c r="E713" s="6" t="s">
         <v>167</v>
       </c>
@@ -24717,14 +24695,12 @@
         <v>1538</v>
       </c>
       <c r="B714" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C714" s="7" t="s">
         <v>1539</v>
       </c>
-      <c r="D714" s="11">
-        <v>2.5538E7</v>
-      </c>
+      <c r="D714" s="11"/>
       <c r="E714" s="6" t="s">
         <v>167</v>
       </c>
@@ -24746,7 +24722,7 @@
         <v>1540</v>
       </c>
       <c r="B715" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C715" s="7" t="s">
         <v>1541</v>
@@ -24769,7 +24745,7 @@
         <v>1542</v>
       </c>
       <c r="B716" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C716" s="7" t="s">
         <v>1543</v>
@@ -24792,7 +24768,7 @@
         <v>1544</v>
       </c>
       <c r="B717" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C717" s="7" t="s">
         <v>1545</v>
@@ -24815,7 +24791,7 @@
         <v>1546</v>
       </c>
       <c r="B718" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C718" s="7" t="s">
         <v>1547</v>
@@ -24840,7 +24816,7 @@
         <v>1548</v>
       </c>
       <c r="B719" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C719" s="7" t="s">
         <v>1549</v>
@@ -24865,7 +24841,7 @@
         <v>1550</v>
       </c>
       <c r="B720" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C720" s="7" t="s">
         <v>1551</v>
@@ -24890,7 +24866,7 @@
         <v>1552</v>
       </c>
       <c r="B721" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C721" s="7" t="s">
         <v>1553</v>
@@ -24913,7 +24889,7 @@
         <v>1554</v>
       </c>
       <c r="B722" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C722" s="7" t="s">
         <v>1555</v>
@@ -24936,7 +24912,7 @@
         <v>1556</v>
       </c>
       <c r="B723" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C723" s="7" t="s">
         <v>1557</v>
@@ -24959,7 +24935,7 @@
         <v>1558</v>
       </c>
       <c r="B724" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C724" s="7" t="s">
         <v>1559</v>
@@ -24982,7 +24958,7 @@
         <v>1560</v>
       </c>
       <c r="B725" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C725" s="7" t="s">
         <v>1561</v>
@@ -25005,7 +24981,7 @@
         <v>1562</v>
       </c>
       <c r="B726" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C726" s="7" t="s">
         <v>1563</v>
@@ -25028,7 +25004,7 @@
         <v>1564</v>
       </c>
       <c r="B727" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C727" s="7" t="s">
         <v>1565</v>
@@ -25051,7 +25027,7 @@
         <v>1566</v>
       </c>
       <c r="B728" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C728" s="7" t="s">
         <v>1567</v>
@@ -25074,7 +25050,7 @@
         <v>1568</v>
       </c>
       <c r="B729" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C729" s="7" t="s">
         <v>1569</v>
@@ -25097,7 +25073,7 @@
         <v>1570</v>
       </c>
       <c r="B730" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C730" s="7" t="s">
         <v>1571</v>
@@ -25120,7 +25096,7 @@
         <v>1572</v>
       </c>
       <c r="B731" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C731" s="7" t="s">
         <v>1573</v>
@@ -25147,14 +25123,12 @@
         <v>1574</v>
       </c>
       <c r="B732" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C732" s="7" t="s">
         <v>1575</v>
       </c>
-      <c r="D732" s="11">
-        <v>3108000.0</v>
-      </c>
+      <c r="D732" s="11"/>
       <c r="E732" s="6" t="s">
         <v>632</v>
       </c>
@@ -25176,7 +25150,7 @@
         <v>1578</v>
       </c>
       <c r="B733" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C733" s="7" t="s">
         <v>1579</v>
@@ -25201,7 +25175,7 @@
         <v>1580</v>
       </c>
       <c r="B734" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C734" s="7" t="s">
         <v>1581</v>
@@ -25224,7 +25198,7 @@
         <v>1582</v>
       </c>
       <c r="B735" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C735" s="7" t="s">
         <v>1583</v>
@@ -25249,7 +25223,7 @@
         <v>1584</v>
       </c>
       <c r="B736" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C736" s="7" t="s">
         <v>1585</v>
@@ -25272,7 +25246,7 @@
         <v>1586</v>
       </c>
       <c r="B737" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C737" s="7" t="s">
         <v>1587</v>
@@ -25295,7 +25269,7 @@
         <v>1588</v>
       </c>
       <c r="B738" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C738" s="7" t="s">
         <v>1589</v>
@@ -25318,7 +25292,7 @@
         <v>1590</v>
       </c>
       <c r="B739" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C739" s="7" t="s">
         <v>1591</v>
@@ -25343,7 +25317,7 @@
         <v>1592</v>
       </c>
       <c r="B740" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C740" s="7" t="s">
         <v>1593</v>
@@ -25368,7 +25342,7 @@
         <v>1594</v>
       </c>
       <c r="B741" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C741" s="7" t="s">
         <v>1595</v>
@@ -25393,7 +25367,7 @@
         <v>1596</v>
       </c>
       <c r="B742" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C742" s="7" t="s">
         <v>1597</v>
@@ -25418,7 +25392,7 @@
         <v>1598</v>
       </c>
       <c r="B743" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C743" s="7" t="s">
         <v>1599</v>
@@ -25443,7 +25417,7 @@
         <v>1600</v>
       </c>
       <c r="B744" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C744" s="7" t="s">
         <v>1601</v>
@@ -25611,9 +25585,7 @@
       <c r="C751" s="7" t="s">
         <v>1619</v>
       </c>
-      <c r="D751" s="11">
-        <v>2498000.0</v>
-      </c>
+      <c r="D751" s="11"/>
       <c r="E751" s="6" t="s">
         <v>167</v>
       </c>
@@ -26001,9 +25973,7 @@
       <c r="C767" s="7" t="s">
         <v>1653</v>
       </c>
-      <c r="D767" s="11">
-        <v>7.4579E7</v>
-      </c>
+      <c r="D767" s="11"/>
       <c r="E767" s="6" t="s">
         <v>33</v>
       </c>
@@ -26026,9 +25996,7 @@
       <c r="C768" s="7" t="s">
         <v>1655</v>
       </c>
-      <c r="D768" s="11">
-        <v>7.4579E7</v>
-      </c>
+      <c r="D768" s="11"/>
       <c r="E768" s="6" t="s">
         <v>33</v>
       </c>
@@ -26074,9 +26042,7 @@
       <c r="C770" s="7" t="s">
         <v>1659</v>
       </c>
-      <c r="D770" s="11">
-        <v>1.25429E8</v>
-      </c>
+      <c r="D770" s="11"/>
       <c r="E770" s="6" t="s">
         <v>33</v>
       </c>
@@ -26101,9 +26067,7 @@
       <c r="C771" s="7" t="s">
         <v>1662</v>
       </c>
-      <c r="D771" s="11">
-        <v>1.25429E8</v>
-      </c>
+      <c r="D771" s="11"/>
       <c r="E771" s="6" t="s">
         <v>33</v>
       </c>
@@ -26128,9 +26092,7 @@
       <c r="C772" s="7" t="s">
         <v>1664</v>
       </c>
-      <c r="D772" s="11">
-        <v>1.25429E8</v>
-      </c>
+      <c r="D772" s="11"/>
       <c r="E772" s="6" t="s">
         <v>33</v>
       </c>
@@ -26155,9 +26117,7 @@
       <c r="C773" s="7" t="s">
         <v>1666</v>
       </c>
-      <c r="D773" s="11">
-        <v>1.25429E8</v>
-      </c>
+      <c r="D773" s="11"/>
       <c r="E773" s="6" t="s">
         <v>33</v>
       </c>
@@ -26182,9 +26142,7 @@
       <c r="C774" s="7" t="s">
         <v>1668</v>
       </c>
-      <c r="D774" s="11">
-        <v>1.57069E8</v>
-      </c>
+      <c r="D774" s="11"/>
       <c r="E774" s="6" t="s">
         <v>33</v>
       </c>
@@ -26263,9 +26221,7 @@
       <c r="C777" s="7" t="s">
         <v>1677</v>
       </c>
-      <c r="D777" s="11">
-        <v>1.1865E7</v>
-      </c>
+      <c r="D777" s="11"/>
       <c r="E777" s="6" t="s">
         <v>632</v>
       </c>
@@ -26319,9 +26275,7 @@
       <c r="C779" s="7" t="s">
         <v>1685</v>
       </c>
-      <c r="D779" s="11">
-        <v>8927000.0</v>
-      </c>
+      <c r="D779" s="11"/>
       <c r="E779" s="6" t="s">
         <v>632</v>
       </c>
@@ -26394,9 +26348,7 @@
       <c r="C782" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="D782" s="11">
-        <v>1.1865E8</v>
-      </c>
+      <c r="D782" s="11"/>
       <c r="E782" s="6" t="s">
         <v>1347</v>
       </c>
@@ -26448,9 +26400,7 @@
       <c r="C784" s="7" t="s">
         <v>1701</v>
       </c>
-      <c r="D784" s="11">
-        <v>8.8705E7</v>
-      </c>
+      <c r="D784" s="11"/>
       <c r="E784" s="6" t="s">
         <v>1347</v>
       </c>
@@ -26477,9 +26427,7 @@
       <c r="C785" s="7" t="s">
         <v>1703</v>
       </c>
-      <c r="D785" s="11">
-        <v>6.328E7</v>
-      </c>
+      <c r="D785" s="11"/>
       <c r="E785" s="6" t="s">
         <v>1347</v>
       </c>
@@ -27271,9 +27219,7 @@
       <c r="C819" s="7" t="s">
         <v>1778</v>
       </c>
-      <c r="D819" s="11">
-        <v>1.85319E8</v>
-      </c>
+      <c r="D819" s="11"/>
       <c r="E819" s="6" t="s">
         <v>33</v>
       </c>
@@ -28479,9 +28425,7 @@
       <c r="C869" s="7" t="s">
         <v>1863</v>
       </c>
-      <c r="D869" s="11">
-        <v>6.1019E7</v>
-      </c>
+      <c r="D869" s="11"/>
       <c r="E869" s="6" t="s">
         <v>33</v>
       </c>
@@ -28748,9 +28692,7 @@
       <c r="C880" s="7" t="s">
         <v>1885</v>
       </c>
-      <c r="D880" s="11">
-        <v>1.33339E8</v>
-      </c>
+      <c r="D880" s="11"/>
       <c r="E880" s="6" t="s">
         <v>33</v>
       </c>
@@ -29046,9 +28988,7 @@
       <c r="C892" s="7" t="s">
         <v>1909</v>
       </c>
-      <c r="D892" s="11">
-        <v>1.7289E8</v>
-      </c>
+      <c r="D892" s="11"/>
       <c r="E892" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29075,9 +29015,7 @@
       <c r="C893" s="7" t="s">
         <v>1913</v>
       </c>
-      <c r="D893" s="11">
-        <v>1.4803E7</v>
-      </c>
+      <c r="D893" s="11"/>
       <c r="E893" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29104,9 +29042,7 @@
       <c r="C894" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="D894" s="11">
-        <v>9368000.0</v>
-      </c>
+      <c r="D894" s="11"/>
       <c r="E894" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29179,9 +29115,7 @@
       <c r="C897" s="7" t="s">
         <v>1927</v>
       </c>
-      <c r="D897" s="11">
-        <v>1.4916E7</v>
-      </c>
+      <c r="D897" s="11"/>
       <c r="E897" s="6" t="s">
         <v>1339</v>
       </c>
@@ -30050,9 +29984,7 @@
       <c r="C934" s="7" t="s">
         <v>1995</v>
       </c>
-      <c r="D934" s="11">
-        <v>8927000.0</v>
-      </c>
+      <c r="D934" s="11"/>
       <c r="E934" s="6" t="s">
         <v>1608</v>
       </c>
@@ -30612,9 +30544,7 @@
       <c r="C958" s="7" t="s">
         <v>2059</v>
       </c>
-      <c r="D958" s="11">
-        <v>3955000.0</v>
-      </c>
+      <c r="D958" s="11"/>
       <c r="E958" s="6" t="s">
         <v>632</v>
       </c>
@@ -31241,9 +31171,7 @@
       <c r="C985" s="7" t="s">
         <v>2122</v>
       </c>
-      <c r="D985" s="11">
-        <v>5.4579E7</v>
-      </c>
+      <c r="D985" s="11"/>
       <c r="E985" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31270,9 +31198,7 @@
       <c r="C986" s="7" t="s">
         <v>2126</v>
       </c>
-      <c r="D986" s="11">
-        <v>4.0567E7</v>
-      </c>
+      <c r="D986" s="11"/>
       <c r="E986" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31322,9 +31248,7 @@
       <c r="C988" s="7" t="s">
         <v>2131</v>
       </c>
-      <c r="D988" s="11">
-        <v>9492000.0</v>
-      </c>
+      <c r="D988" s="11"/>
       <c r="E988" s="6" t="s">
         <v>632</v>
       </c>
@@ -31405,9 +31329,7 @@
       <c r="C991" s="7" t="s">
         <v>2143</v>
       </c>
-      <c r="D991" s="11">
-        <v>6554000.0</v>
-      </c>
+      <c r="D991" s="11"/>
       <c r="E991" s="6" t="s">
         <v>632</v>
       </c>
@@ -31484,9 +31406,7 @@
       <c r="C994" s="7" t="s">
         <v>2150</v>
       </c>
-      <c r="D994" s="11">
-        <v>8475000.0</v>
-      </c>
+      <c r="D994" s="11"/>
       <c r="E994" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31561,9 +31481,7 @@
       <c r="C997" s="7" t="s">
         <v>2157</v>
       </c>
-      <c r="D997" s="11">
-        <v>7.797E7</v>
-      </c>
+      <c r="D997" s="11"/>
       <c r="E997" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31636,9 +31554,7 @@
       <c r="C1000" s="7" t="s">
         <v>2165</v>
       </c>
-      <c r="D1000" s="11">
-        <v>8.7009E7</v>
-      </c>
+      <c r="D1000" s="11"/>
       <c r="E1000" s="6" t="s">
         <v>1347</v>
       </c>
@@ -31807,9 +31723,7 @@
       <c r="C1007" s="7" t="s">
         <v>2185</v>
       </c>
-      <c r="D1007" s="11">
-        <v>4.2939E7</v>
-      </c>
+      <c r="D1007" s="11"/>
       <c r="E1007" s="6" t="s">
         <v>167</v>
       </c>
@@ -31836,9 +31750,7 @@
       <c r="C1008" s="7" t="s">
         <v>2189</v>
       </c>
-      <c r="D1008" s="11">
-        <v>6102000.0</v>
-      </c>
+      <c r="D1008" s="11"/>
       <c r="E1008" s="6" t="s">
         <v>167</v>
       </c>
@@ -31936,9 +31848,7 @@
       <c r="C1012" s="7" t="s">
         <v>2199</v>
       </c>
-      <c r="D1012" s="11">
-        <v>3615000.0</v>
-      </c>
+      <c r="D1012" s="11"/>
       <c r="E1012" s="6" t="s">
         <v>33</v>
       </c>
@@ -31965,9 +31875,7 @@
       <c r="C1013" s="7" t="s">
         <v>2201</v>
       </c>
-      <c r="D1013" s="11">
-        <v>4745000.0</v>
-      </c>
+      <c r="D1013" s="11"/>
       <c r="E1013" s="6" t="s">
         <v>33</v>
       </c>
@@ -31994,9 +31902,7 @@
       <c r="C1014" s="7" t="s">
         <v>2203</v>
       </c>
-      <c r="D1014" s="11">
-        <v>8135000.0</v>
-      </c>
+      <c r="D1014" s="11"/>
       <c r="E1014" s="6" t="s">
         <v>33</v>
       </c>
@@ -32069,9 +31975,7 @@
       <c r="C1017" s="7" t="s">
         <v>2209</v>
       </c>
-      <c r="D1017" s="11">
-        <v>3.0509E7</v>
-      </c>
+      <c r="D1017" s="11"/>
       <c r="E1017" s="6" t="s">
         <v>33</v>
       </c>
@@ -32098,9 +32002,7 @@
       <c r="C1018" s="7" t="s">
         <v>2212</v>
       </c>
-      <c r="D1018" s="11">
-        <v>3.0509E7</v>
-      </c>
+      <c r="D1018" s="11"/>
       <c r="E1018" s="6" t="s">
         <v>33</v>
       </c>
@@ -32127,9 +32029,7 @@
       <c r="C1019" s="7" t="s">
         <v>2214</v>
       </c>
-      <c r="D1019" s="11">
-        <v>3.0509E7</v>
-      </c>
+      <c r="D1019" s="11"/>
       <c r="E1019" s="6" t="s">
         <v>33</v>
       </c>
@@ -32156,9 +32056,7 @@
       <c r="C1020" s="7" t="s">
         <v>2216</v>
       </c>
-      <c r="D1020" s="11">
-        <v>6.2149E7</v>
-      </c>
+      <c r="D1020" s="11"/>
       <c r="E1020" s="6" t="s">
         <v>33</v>
       </c>
@@ -32185,9 +32083,7 @@
       <c r="C1021" s="7" t="s">
         <v>2220</v>
       </c>
-      <c r="D1021" s="11">
-        <v>6.2149E7</v>
-      </c>
+      <c r="D1021" s="11"/>
       <c r="E1021" s="6" t="s">
         <v>33</v>
       </c>
@@ -32241,9 +32137,7 @@
       <c r="C1023" s="7" t="s">
         <v>2224</v>
       </c>
-      <c r="D1023" s="11">
-        <v>7.1189E7</v>
-      </c>
+      <c r="D1023" s="11"/>
       <c r="E1023" s="6" t="s">
         <v>33</v>
       </c>
@@ -32270,9 +32164,7 @@
       <c r="C1024" s="7" t="s">
         <v>2227</v>
       </c>
-      <c r="D1024" s="11">
-        <v>7.1189E7</v>
-      </c>
+      <c r="D1024" s="11"/>
       <c r="E1024" s="6" t="s">
         <v>33</v>
       </c>
@@ -32299,9 +32191,7 @@
       <c r="C1025" s="7" t="s">
         <v>2229</v>
       </c>
-      <c r="D1025" s="11">
-        <v>7.1189E7</v>
-      </c>
+      <c r="D1025" s="11"/>
       <c r="E1025" s="6" t="s">
         <v>33</v>
       </c>
@@ -32328,9 +32218,7 @@
       <c r="C1026" s="7" t="s">
         <v>2231</v>
       </c>
-      <c r="D1026" s="11">
-        <v>8.5879E7</v>
-      </c>
+      <c r="D1026" s="11"/>
       <c r="E1026" s="6" t="s">
         <v>33</v>
       </c>
@@ -32357,9 +32245,7 @@
       <c r="C1027" s="7" t="s">
         <v>2235</v>
       </c>
-      <c r="D1027" s="11">
-        <v>8.5879E7</v>
-      </c>
+      <c r="D1027" s="11"/>
       <c r="E1027" s="6" t="s">
         <v>33</v>
       </c>
@@ -32386,9 +32272,7 @@
       <c r="C1028" s="7" t="s">
         <v>2237</v>
       </c>
-      <c r="D1028" s="11">
-        <v>8.5879E7</v>
-      </c>
+      <c r="D1028" s="11"/>
       <c r="E1028" s="6" t="s">
         <v>33</v>
       </c>
@@ -32415,9 +32299,7 @@
       <c r="C1029" s="7" t="s">
         <v>2239</v>
       </c>
-      <c r="D1029" s="11">
-        <v>8.8817E7</v>
-      </c>
+      <c r="D1029" s="11"/>
       <c r="E1029" s="6" t="s">
         <v>33</v>
       </c>
@@ -32442,9 +32324,7 @@
       <c r="C1030" s="7" t="s">
         <v>2241</v>
       </c>
-      <c r="D1030" s="11">
-        <v>8.8817E7</v>
-      </c>
+      <c r="D1030" s="11"/>
       <c r="E1030" s="6" t="s">
         <v>33</v>
       </c>
@@ -32498,9 +32378,7 @@
       <c r="C1032" s="7" t="s">
         <v>2248</v>
       </c>
-      <c r="D1032" s="11">
-        <v>1.70629E8</v>
-      </c>
+      <c r="D1032" s="11"/>
       <c r="E1032" s="6" t="s">
         <v>33</v>
       </c>
@@ -32552,9 +32430,7 @@
       <c r="C1034" s="7" t="s">
         <v>2252</v>
       </c>
-      <c r="D1034" s="11">
-        <v>1.77409E8</v>
-      </c>
+      <c r="D1034" s="11"/>
       <c r="E1034" s="6" t="s">
         <v>33</v>
       </c>
@@ -32581,9 +32457,7 @@
       <c r="C1035" s="7" t="s">
         <v>2255</v>
       </c>
-      <c r="D1035" s="11">
-        <v>1.77409E8</v>
-      </c>
+      <c r="D1035" s="11"/>
       <c r="E1035" s="6" t="s">
         <v>33</v>
       </c>
@@ -32610,9 +32484,7 @@
       <c r="C1036" s="7" t="s">
         <v>2257</v>
       </c>
-      <c r="D1036" s="11">
-        <v>1.77409E8</v>
-      </c>
+      <c r="D1036" s="11"/>
       <c r="E1036" s="6" t="s">
         <v>33</v>
       </c>
@@ -32639,9 +32511,7 @@
       <c r="C1037" s="7" t="s">
         <v>2259</v>
       </c>
-      <c r="D1037" s="11">
-        <v>9.7179E7</v>
-      </c>
+      <c r="D1037" s="11"/>
       <c r="E1037" s="6" t="s">
         <v>33</v>
       </c>
@@ -32668,9 +32538,7 @@
       <c r="C1038" s="7" t="s">
         <v>2263</v>
       </c>
-      <c r="D1038" s="11">
-        <v>9.7179E7</v>
-      </c>
+      <c r="D1038" s="11"/>
       <c r="E1038" s="6" t="s">
         <v>33</v>
       </c>
@@ -32724,9 +32592,7 @@
       <c r="C1040" s="7" t="s">
         <v>2268</v>
       </c>
-      <c r="D1040" s="11">
-        <v>9.9439E7</v>
-      </c>
+      <c r="D1040" s="11"/>
       <c r="E1040" s="6" t="s">
         <v>33</v>
       </c>
@@ -32753,9 +32619,7 @@
       <c r="C1041" s="7" t="s">
         <v>2270</v>
       </c>
-      <c r="D1041" s="11">
-        <v>9.9439E7</v>
-      </c>
+      <c r="D1041" s="11"/>
       <c r="E1041" s="6" t="s">
         <v>33</v>
       </c>
@@ -33378,7 +33242,7 @@
         <v>2321</v>
       </c>
       <c r="B1067" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1067" s="7" t="s">
         <v>2322</v>
@@ -33756,7 +33620,7 @@
         <v>2353</v>
       </c>
       <c r="B1083" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1083" s="7" t="s">
         <v>2354</v>
@@ -34065,9 +33929,7 @@
       <c r="C1095" s="7" t="s">
         <v>2385</v>
       </c>
-      <c r="D1095" s="11">
-        <v>1.15104E8</v>
-      </c>
+      <c r="D1095" s="11"/>
       <c r="E1095" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34175,9 +34037,7 @@
       <c r="C1099" s="7" t="s">
         <v>2398</v>
       </c>
-      <c r="D1099" s="11">
-        <v>1.451516E8</v>
-      </c>
+      <c r="D1099" s="11"/>
       <c r="E1099" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34231,9 +34091,7 @@
       <c r="C1101" s="7" t="s">
         <v>2406</v>
       </c>
-      <c r="D1101" s="11">
-        <v>1.013727E8</v>
-      </c>
+      <c r="D1101" s="11"/>
       <c r="E1101" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34260,9 +34118,7 @@
       <c r="C1102" s="7" t="s">
         <v>2409</v>
       </c>
-      <c r="D1102" s="11">
-        <v>6.456681E7</v>
-      </c>
+      <c r="D1102" s="11"/>
       <c r="E1102" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34289,9 +34145,7 @@
       <c r="C1103" s="7" t="s">
         <v>2412</v>
       </c>
-      <c r="D1103" s="11">
-        <v>2.5696E7</v>
-      </c>
+      <c r="D1103" s="11"/>
       <c r="E1103" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34318,9 +34172,7 @@
       <c r="C1104" s="7" t="s">
         <v>2417</v>
       </c>
-      <c r="D1104" s="11">
-        <v>2.56344E7</v>
-      </c>
+      <c r="D1104" s="11"/>
       <c r="E1104" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34347,9 +34199,7 @@
       <c r="C1105" s="7" t="s">
         <v>2421</v>
       </c>
-      <c r="D1105" s="11">
-        <v>2.53506E7</v>
-      </c>
+      <c r="D1105" s="11"/>
       <c r="E1105" s="6" t="s">
         <v>1608</v>
       </c>
@@ -39527,91 +39377,91 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="33.0" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="33.0" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="33.0" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="33.0" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="33.0" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="33.0" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="B8" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" ht="33.0" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="33.0" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -73,36 +73,36 @@
     <t>نمایش محصول</t>
   </si>
   <si>
+    <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
+  </si>
+  <si>
     <t>برند</t>
   </si>
   <si>
-    <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
+    <t>موجود کردن</t>
+  </si>
+  <si>
+    <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
   </si>
   <si>
     <t>کد محصول</t>
   </si>
   <si>
-    <t>موجود کردن</t>
-  </si>
-  <si>
-    <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
-  </si>
-  <si>
     <t>ناموجود کردن</t>
   </si>
   <si>
     <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
   </si>
   <si>
+    <t>فهرست برندها</t>
+  </si>
+  <si>
+    <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
+  </si>
+  <si>
     <t>قیمت نقد</t>
   </si>
   <si>
-    <t>فهرست برندها</t>
-  </si>
-  <si>
-    <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
-  </si>
-  <si>
     <t>عکس محصول</t>
   </si>
   <si>
@@ -112,43 +112,43 @@
     <t>توضیحات</t>
   </si>
   <si>
+    <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
+  </si>
+  <si>
+    <t>آرایشی و بهداشتی</t>
+  </si>
+  <si>
     <t>دسته‌بندی</t>
   </si>
   <si>
-    <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
-  </si>
-  <si>
-    <t>آرایشی و بهداشتی</t>
-  </si>
-  <si>
     <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
   </si>
   <si>
     <t>دسته‌بندی‌های مجاز</t>
   </si>
   <si>
+    <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
+  </si>
+  <si>
+    <t>پوشه عکس محصولات</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
     <t>عکس</t>
   </si>
   <si>
-    <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
-  </si>
-  <si>
-    <t>پوشه عکس محصولات</t>
+    <t>پوشه بنرها</t>
+  </si>
+  <si>
+    <t>baner</t>
   </si>
   <si>
     <t>دسته‌بندی اصلی</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
     <t>گروه اصلی</t>
-  </si>
-  <si>
-    <t>پوشه بنرها</t>
-  </si>
-  <si>
-    <t>baner</t>
   </si>
   <si>
     <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
@@ -8048,28 +8048,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" hidden="1">
@@ -8253,7 +8253,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9">
       <c r="A9" s="5" t="s">
         <v>51</v>
       </c>
@@ -8263,7 +8263,9 @@
       <c r="C9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8">
+        <v>4.85889E8</v>
+      </c>
       <c r="E9" s="6" t="s">
         <v>33</v>
       </c>
@@ -24646,9 +24648,7 @@
       <c r="C712" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="D712" s="8">
-        <v>4.9155E7</v>
-      </c>
+      <c r="D712" s="8"/>
       <c r="E712" s="6" t="s">
         <v>167</v>
       </c>
@@ -24675,9 +24675,7 @@
       <c r="C713" s="7" t="s">
         <v>1537</v>
       </c>
-      <c r="D713" s="8">
-        <v>3.7516E7</v>
-      </c>
+      <c r="D713" s="8"/>
       <c r="E713" s="6" t="s">
         <v>167</v>
       </c>
@@ -24704,9 +24702,7 @@
       <c r="C714" s="7" t="s">
         <v>1539</v>
       </c>
-      <c r="D714" s="8">
-        <v>2.6894E7</v>
-      </c>
+      <c r="D714" s="8"/>
       <c r="E714" s="6" t="s">
         <v>167</v>
       </c>
@@ -25107,9 +25103,7 @@
       <c r="C731" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="D731" s="8">
-        <v>3.7855E7</v>
-      </c>
+      <c r="D731" s="8"/>
       <c r="E731" s="6" t="s">
         <v>167</v>
       </c>
@@ -25136,9 +25130,7 @@
       <c r="C732" s="7" t="s">
         <v>1575</v>
       </c>
-      <c r="D732" s="8">
-        <v>3277000.0</v>
-      </c>
+      <c r="D732" s="8"/>
       <c r="E732" s="6" t="s">
         <v>632</v>
       </c>
@@ -25595,9 +25587,7 @@
       <c r="C751" s="7" t="s">
         <v>1619</v>
       </c>
-      <c r="D751" s="8">
-        <v>2543000.0</v>
-      </c>
+      <c r="D751" s="8"/>
       <c r="E751" s="6" t="s">
         <v>167</v>
       </c>
@@ -25985,9 +25975,7 @@
       <c r="C767" s="7" t="s">
         <v>1653</v>
       </c>
-      <c r="D767" s="8">
-        <v>8.5879E7</v>
-      </c>
+      <c r="D767" s="8"/>
       <c r="E767" s="6" t="s">
         <v>33</v>
       </c>
@@ -26010,9 +25998,7 @@
       <c r="C768" s="7" t="s">
         <v>1655</v>
       </c>
-      <c r="D768" s="8">
-        <v>8.5879E7</v>
-      </c>
+      <c r="D768" s="8"/>
       <c r="E768" s="6" t="s">
         <v>33</v>
       </c>
@@ -26058,9 +26044,7 @@
       <c r="C770" s="7" t="s">
         <v>1659</v>
       </c>
-      <c r="D770" s="8">
-        <v>1.32209E8</v>
-      </c>
+      <c r="D770" s="8"/>
       <c r="E770" s="6" t="s">
         <v>33</v>
       </c>
@@ -26085,9 +26069,7 @@
       <c r="C771" s="7" t="s">
         <v>1662</v>
       </c>
-      <c r="D771" s="8">
-        <v>1.32209E8</v>
-      </c>
+      <c r="D771" s="8"/>
       <c r="E771" s="6" t="s">
         <v>33</v>
       </c>
@@ -26112,9 +26094,7 @@
       <c r="C772" s="7" t="s">
         <v>1664</v>
       </c>
-      <c r="D772" s="8">
-        <v>1.32209E8</v>
-      </c>
+      <c r="D772" s="8"/>
       <c r="E772" s="6" t="s">
         <v>33</v>
       </c>
@@ -26139,9 +26119,7 @@
       <c r="C773" s="7" t="s">
         <v>1666</v>
       </c>
-      <c r="D773" s="8">
-        <v>1.32209E8</v>
-      </c>
+      <c r="D773" s="8"/>
       <c r="E773" s="6" t="s">
         <v>33</v>
       </c>
@@ -26166,9 +26144,7 @@
       <c r="C774" s="7" t="s">
         <v>1668</v>
       </c>
-      <c r="D774" s="8">
-        <v>1.60459E8</v>
-      </c>
+      <c r="D774" s="8"/>
       <c r="E774" s="6" t="s">
         <v>33</v>
       </c>
@@ -26237,7 +26213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="777">
+    <row r="777" hidden="1">
       <c r="A777" s="6" t="s">
         <v>1675</v>
       </c>
@@ -26247,9 +26223,7 @@
       <c r="C777" s="7" t="s">
         <v>1677</v>
       </c>
-      <c r="D777" s="8">
-        <v>1.1865E7</v>
-      </c>
+      <c r="D777" s="8"/>
       <c r="E777" s="6" t="s">
         <v>632</v>
       </c>
@@ -26293,7 +26267,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="779">
+    <row r="779" hidden="1">
       <c r="A779" s="6" t="s">
         <v>1684</v>
       </c>
@@ -26303,9 +26277,7 @@
       <c r="C779" s="7" t="s">
         <v>1685</v>
       </c>
-      <c r="D779" s="8">
-        <v>9153000.0</v>
-      </c>
+      <c r="D779" s="8"/>
       <c r="E779" s="6" t="s">
         <v>632</v>
       </c>
@@ -26368,7 +26340,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="782">
+    <row r="782" hidden="1">
       <c r="A782" s="6" t="s">
         <v>1693</v>
       </c>
@@ -26378,9 +26350,7 @@
       <c r="C782" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="D782" s="8">
-        <v>1.19554E8</v>
-      </c>
+      <c r="D782" s="8"/>
       <c r="E782" s="6" t="s">
         <v>1347</v>
       </c>
@@ -26422,7 +26392,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="784">
+    <row r="784" hidden="1">
       <c r="A784" s="6" t="s">
         <v>1700</v>
       </c>
@@ -26432,9 +26402,7 @@
       <c r="C784" s="7" t="s">
         <v>1701</v>
       </c>
-      <c r="D784" s="8">
-        <v>8.9496E7</v>
-      </c>
+      <c r="D784" s="8"/>
       <c r="E784" s="6" t="s">
         <v>1347</v>
       </c>
@@ -26451,7 +26419,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="785">
+    <row r="785" hidden="1">
       <c r="A785" s="6" t="s">
         <v>1702</v>
       </c>
@@ -26461,9 +26429,7 @@
       <c r="C785" s="7" t="s">
         <v>1703</v>
       </c>
-      <c r="D785" s="8">
-        <v>6.78E7</v>
-      </c>
+      <c r="D785" s="8"/>
       <c r="E785" s="6" t="s">
         <v>1347</v>
       </c>
@@ -27245,7 +27211,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="819" hidden="1">
+    <row r="819">
       <c r="A819" s="5" t="s">
         <v>1777</v>
       </c>
@@ -28125,9 +28091,7 @@
       <c r="C855" s="7" t="s">
         <v>1835</v>
       </c>
-      <c r="D855" s="8">
-        <v>1.01699E8</v>
-      </c>
+      <c r="D855" s="8"/>
       <c r="E855" s="6" t="s">
         <v>33</v>
       </c>
@@ -28367,9 +28331,7 @@
       <c r="C865" s="7" t="s">
         <v>1854</v>
       </c>
-      <c r="D865" s="8">
-        <v>1.17519E8</v>
-      </c>
+      <c r="D865" s="8"/>
       <c r="E865" s="6" t="s">
         <v>33</v>
       </c>
@@ -28484,7 +28446,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="870" hidden="1">
+    <row r="870">
       <c r="A870" s="5" t="s">
         <v>1865</v>
       </c>
@@ -28590,9 +28552,7 @@
       <c r="C874" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="D874" s="8">
-        <v>8.8139E7</v>
-      </c>
+      <c r="D874" s="8"/>
       <c r="E874" s="6" t="s">
         <v>33</v>
       </c>
@@ -28728,7 +28688,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="880" hidden="1">
+    <row r="880">
       <c r="A880" s="5" t="s">
         <v>1498</v>
       </c>
@@ -28738,9 +28698,7 @@
       <c r="C880" s="7" t="s">
         <v>1885</v>
       </c>
-      <c r="D880" s="8">
-        <v>1.55939E8</v>
-      </c>
+      <c r="D880" s="8"/>
       <c r="E880" s="6" t="s">
         <v>33</v>
       </c>
@@ -28782,7 +28740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="882" hidden="1">
+    <row r="882">
       <c r="A882" s="5" t="s">
         <v>545</v>
       </c>
@@ -28792,9 +28750,7 @@
       <c r="C882" s="7" t="s">
         <v>1889</v>
       </c>
-      <c r="D882" s="8">
-        <v>1.24299E8</v>
-      </c>
+      <c r="D882" s="8"/>
       <c r="E882" s="6" t="s">
         <v>33</v>
       </c>
@@ -29028,7 +28984,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="892">
+    <row r="892" hidden="1">
       <c r="A892" s="5" t="s">
         <v>1908</v>
       </c>
@@ -29038,9 +28994,7 @@
       <c r="C892" s="7" t="s">
         <v>1909</v>
       </c>
-      <c r="D892" s="8">
-        <v>1.7402E8</v>
-      </c>
+      <c r="D892" s="8"/>
       <c r="E892" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29057,7 +29011,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="893">
+    <row r="893" hidden="1">
       <c r="A893" s="6" t="s">
         <v>1912</v>
       </c>
@@ -29067,9 +29021,7 @@
       <c r="C893" s="7" t="s">
         <v>1913</v>
       </c>
-      <c r="D893" s="8">
-        <v>1.5029E7</v>
-      </c>
+      <c r="D893" s="8"/>
       <c r="E893" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29086,7 +29038,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="894">
+    <row r="894" hidden="1">
       <c r="A894" s="6" t="s">
         <v>1917</v>
       </c>
@@ -29096,9 +29048,7 @@
       <c r="C894" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="D894" s="8">
-        <v>9323000.0</v>
-      </c>
+      <c r="D894" s="8"/>
       <c r="E894" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29161,7 +29111,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="897">
+    <row r="897" hidden="1">
       <c r="A897" s="6" t="s">
         <v>1926</v>
       </c>
@@ -29171,9 +29121,7 @@
       <c r="C897" s="7" t="s">
         <v>1927</v>
       </c>
-      <c r="D897" s="8">
-        <v>1.5142E7</v>
-      </c>
+      <c r="D897" s="8"/>
       <c r="E897" s="6" t="s">
         <v>1339</v>
       </c>
@@ -29292,9 +29240,7 @@
       <c r="C902" s="7" t="s">
         <v>1937</v>
       </c>
-      <c r="D902" s="8">
-        <v>9.0399E7</v>
-      </c>
+      <c r="D902" s="8"/>
       <c r="E902" s="6" t="s">
         <v>33</v>
       </c>
@@ -30034,7 +29980,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="934">
+    <row r="934" hidden="1">
       <c r="A934" s="6" t="s">
         <v>1994</v>
       </c>
@@ -30044,9 +29990,7 @@
       <c r="C934" s="7" t="s">
         <v>1995</v>
       </c>
-      <c r="D934" s="8">
-        <v>9040000.0</v>
-      </c>
+      <c r="D934" s="8"/>
       <c r="E934" s="6" t="s">
         <v>1608</v>
       </c>
@@ -30596,7 +30540,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="958">
+    <row r="958" hidden="1">
       <c r="A958" s="6" t="s">
         <v>2058</v>
       </c>
@@ -30606,9 +30550,7 @@
       <c r="C958" s="7" t="s">
         <v>2059</v>
       </c>
-      <c r="D958" s="8">
-        <v>4068000.0</v>
-      </c>
+      <c r="D958" s="8"/>
       <c r="E958" s="6" t="s">
         <v>632</v>
       </c>
@@ -31189,9 +31131,7 @@
       <c r="C983" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="D983" s="8">
-        <v>8.8139E7</v>
-      </c>
+      <c r="D983" s="8"/>
       <c r="E983" s="6" t="s">
         <v>33</v>
       </c>
@@ -31254,7 +31194,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="986">
+    <row r="986" hidden="1">
       <c r="A986" s="6" t="s">
         <v>2125</v>
       </c>
@@ -31264,9 +31204,7 @@
       <c r="C986" s="7" t="s">
         <v>2126</v>
       </c>
-      <c r="D986" s="8">
-        <v>4.181E7</v>
-      </c>
+      <c r="D986" s="8"/>
       <c r="E986" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31306,7 +31244,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="988">
+    <row r="988" hidden="1">
       <c r="A988" s="6" t="s">
         <v>2130</v>
       </c>
@@ -31316,9 +31254,7 @@
       <c r="C988" s="7" t="s">
         <v>2131</v>
       </c>
-      <c r="D988" s="8">
-        <v>9944000.0</v>
-      </c>
+      <c r="D988" s="8"/>
       <c r="E988" s="6" t="s">
         <v>632</v>
       </c>
@@ -31389,7 +31325,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="991">
+    <row r="991" hidden="1">
       <c r="A991" s="6" t="s">
         <v>2142</v>
       </c>
@@ -31399,9 +31335,7 @@
       <c r="C991" s="7" t="s">
         <v>2143</v>
       </c>
-      <c r="D991" s="8">
-        <v>6780000.0</v>
-      </c>
+      <c r="D991" s="8"/>
       <c r="E991" s="6" t="s">
         <v>632</v>
       </c>
@@ -31468,7 +31402,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="994">
+    <row r="994" hidden="1">
       <c r="A994" s="6" t="s">
         <v>2149</v>
       </c>
@@ -31478,9 +31412,7 @@
       <c r="C994" s="7" t="s">
         <v>2150</v>
       </c>
-      <c r="D994" s="8">
-        <v>8645000.0</v>
-      </c>
+      <c r="D994" s="8"/>
       <c r="E994" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31545,7 +31477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="997">
+    <row r="997" hidden="1">
       <c r="A997" s="6" t="s">
         <v>2156</v>
       </c>
@@ -31555,9 +31487,7 @@
       <c r="C997" s="7" t="s">
         <v>2157</v>
       </c>
-      <c r="D997" s="8">
-        <v>7.91E7</v>
-      </c>
+      <c r="D997" s="8"/>
       <c r="E997" s="6" t="s">
         <v>1608</v>
       </c>
@@ -31620,7 +31550,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="1000">
+    <row r="1000" hidden="1">
       <c r="A1000" s="6" t="s">
         <v>2164</v>
       </c>
@@ -31630,9 +31560,7 @@
       <c r="C1000" s="7" t="s">
         <v>2165</v>
       </c>
-      <c r="D1000" s="8">
-        <v>8.7236E7</v>
-      </c>
+      <c r="D1000" s="8"/>
       <c r="E1000" s="6" t="s">
         <v>1347</v>
       </c>
@@ -31791,7 +31719,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="1007">
+    <row r="1007" hidden="1">
       <c r="A1007" s="6" t="s">
         <v>2184</v>
       </c>
@@ -31801,9 +31729,7 @@
       <c r="C1007" s="7" t="s">
         <v>2185</v>
       </c>
-      <c r="D1007" s="8">
-        <v>4.3166E7</v>
-      </c>
+      <c r="D1007" s="8"/>
       <c r="E1007" s="6" t="s">
         <v>167</v>
       </c>
@@ -31820,7 +31746,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="1008">
+    <row r="1008" hidden="1">
       <c r="A1008" s="6" t="s">
         <v>2188</v>
       </c>
@@ -31830,9 +31756,7 @@
       <c r="C1008" s="7" t="s">
         <v>2189</v>
       </c>
-      <c r="D1008" s="8">
-        <v>6328000.0</v>
-      </c>
+      <c r="D1008" s="8"/>
       <c r="E1008" s="6" t="s">
         <v>167</v>
       </c>
@@ -31930,9 +31854,7 @@
       <c r="C1012" s="7" t="s">
         <v>2199</v>
       </c>
-      <c r="D1012" s="8">
-        <v>3615000.0</v>
-      </c>
+      <c r="D1012" s="8"/>
       <c r="E1012" s="6" t="s">
         <v>33</v>
       </c>
@@ -31959,9 +31881,7 @@
       <c r="C1013" s="7" t="s">
         <v>2201</v>
       </c>
-      <c r="D1013" s="8">
-        <v>4745000.0</v>
-      </c>
+      <c r="D1013" s="8"/>
       <c r="E1013" s="6" t="s">
         <v>33</v>
       </c>
@@ -31988,9 +31908,7 @@
       <c r="C1014" s="7" t="s">
         <v>2203</v>
       </c>
-      <c r="D1014" s="8">
-        <v>8135000.0</v>
-      </c>
+      <c r="D1014" s="8"/>
       <c r="E1014" s="6" t="s">
         <v>33</v>
       </c>
@@ -32063,9 +31981,7 @@
       <c r="C1017" s="7" t="s">
         <v>2209</v>
       </c>
-      <c r="D1017" s="8">
-        <v>3.5029E7</v>
-      </c>
+      <c r="D1017" s="8"/>
       <c r="E1017" s="6" t="s">
         <v>33</v>
       </c>
@@ -32119,9 +32035,7 @@
       <c r="C1019" s="7" t="s">
         <v>2214</v>
       </c>
-      <c r="D1019" s="8">
-        <v>3.5029E7</v>
-      </c>
+      <c r="D1019" s="8"/>
       <c r="E1019" s="6" t="s">
         <v>33</v>
       </c>
@@ -32148,9 +32062,7 @@
       <c r="C1020" s="7" t="s">
         <v>2216</v>
       </c>
-      <c r="D1020" s="8">
-        <v>7.0059E7</v>
-      </c>
+      <c r="D1020" s="8"/>
       <c r="E1020" s="6" t="s">
         <v>33</v>
       </c>
@@ -32312,9 +32224,7 @@
       <c r="C1026" s="7" t="s">
         <v>2231</v>
       </c>
-      <c r="D1026" s="8">
-        <v>9.7179E7</v>
-      </c>
+      <c r="D1026" s="8"/>
       <c r="E1026" s="6" t="s">
         <v>33</v>
       </c>
@@ -32341,9 +32251,7 @@
       <c r="C1027" s="7" t="s">
         <v>2235</v>
       </c>
-      <c r="D1027" s="8">
-        <v>9.7179E7</v>
-      </c>
+      <c r="D1027" s="8"/>
       <c r="E1027" s="6" t="s">
         <v>33</v>
       </c>
@@ -32370,9 +32278,7 @@
       <c r="C1028" s="7" t="s">
         <v>2237</v>
       </c>
-      <c r="D1028" s="8">
-        <v>9.7179E7</v>
-      </c>
+      <c r="D1028" s="8"/>
       <c r="E1028" s="6" t="s">
         <v>33</v>
       </c>
@@ -32399,9 +32305,7 @@
       <c r="C1029" s="7" t="s">
         <v>2239</v>
       </c>
-      <c r="D1029" s="8">
-        <v>1.00569E8</v>
-      </c>
+      <c r="D1029" s="8"/>
       <c r="E1029" s="6" t="s">
         <v>33</v>
       </c>
@@ -32480,9 +32384,7 @@
       <c r="C1032" s="7" t="s">
         <v>2248</v>
       </c>
-      <c r="D1032" s="8">
-        <v>1.76279E8</v>
-      </c>
+      <c r="D1032" s="8"/>
       <c r="E1032" s="6" t="s">
         <v>33</v>
       </c>
@@ -32561,9 +32463,7 @@
       <c r="C1035" s="7" t="s">
         <v>2255</v>
       </c>
-      <c r="D1035" s="8">
-        <v>1.79669E8</v>
-      </c>
+      <c r="D1035" s="8"/>
       <c r="E1035" s="6" t="s">
         <v>33</v>
       </c>
@@ -32590,9 +32490,7 @@
       <c r="C1036" s="7" t="s">
         <v>2257</v>
       </c>
-      <c r="D1036" s="8">
-        <v>1.79669E8</v>
-      </c>
+      <c r="D1036" s="8"/>
       <c r="E1036" s="6" t="s">
         <v>33</v>
       </c>
@@ -32619,9 +32517,7 @@
       <c r="C1037" s="7" t="s">
         <v>2259</v>
       </c>
-      <c r="D1037" s="8">
-        <v>1.06219E8</v>
-      </c>
+      <c r="D1037" s="8"/>
       <c r="E1037" s="6" t="s">
         <v>33</v>
       </c>
@@ -32648,9 +32544,7 @@
       <c r="C1038" s="7" t="s">
         <v>2263</v>
       </c>
-      <c r="D1038" s="8">
-        <v>1.06219E8</v>
-      </c>
+      <c r="D1038" s="8"/>
       <c r="E1038" s="6" t="s">
         <v>33</v>
       </c>
@@ -32704,9 +32598,7 @@
       <c r="C1040" s="7" t="s">
         <v>2268</v>
       </c>
-      <c r="D1040" s="8">
-        <v>1.10739E8</v>
-      </c>
+      <c r="D1040" s="8"/>
       <c r="E1040" s="6" t="s">
         <v>33</v>
       </c>
@@ -32733,9 +32625,7 @@
       <c r="C1041" s="7" t="s">
         <v>2270</v>
       </c>
-      <c r="D1041" s="8">
-        <v>1.10739E8</v>
-      </c>
+      <c r="D1041" s="8"/>
       <c r="E1041" s="6" t="s">
         <v>33</v>
       </c>
@@ -34035,7 +33925,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="1095">
+    <row r="1095" hidden="1">
       <c r="A1095" s="6" t="s">
         <v>2384</v>
       </c>
@@ -34045,9 +33935,7 @@
       <c r="C1095" s="7" t="s">
         <v>2385</v>
       </c>
-      <c r="D1095" s="8">
-        <v>1.15104E8</v>
-      </c>
+      <c r="D1095" s="8"/>
       <c r="E1095" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34145,7 +34033,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="1099">
+    <row r="1099" hidden="1">
       <c r="A1099" s="6" t="s">
         <v>2397</v>
       </c>
@@ -34155,9 +34043,7 @@
       <c r="C1099" s="7" t="s">
         <v>2398</v>
       </c>
-      <c r="D1099" s="8">
-        <v>1.451516E8</v>
-      </c>
+      <c r="D1099" s="8"/>
       <c r="E1099" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34201,7 +34087,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="1101">
+    <row r="1101" hidden="1">
       <c r="A1101" s="6" t="s">
         <v>2405</v>
       </c>
@@ -34211,9 +34097,7 @@
       <c r="C1101" s="7" t="s">
         <v>2406</v>
       </c>
-      <c r="D1101" s="8">
-        <v>1.013727E8</v>
-      </c>
+      <c r="D1101" s="8"/>
       <c r="E1101" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34230,7 +34114,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="1102">
+    <row r="1102" hidden="1">
       <c r="A1102" s="6" t="s">
         <v>2408</v>
       </c>
@@ -34240,9 +34124,7 @@
       <c r="C1102" s="7" t="s">
         <v>2409</v>
       </c>
-      <c r="D1102" s="8">
-        <v>6.456681E7</v>
-      </c>
+      <c r="D1102" s="8"/>
       <c r="E1102" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34259,7 +34141,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="1103">
+    <row r="1103" hidden="1">
       <c r="A1103" s="6" t="s">
         <v>2411</v>
       </c>
@@ -34269,9 +34151,7 @@
       <c r="C1103" s="7" t="s">
         <v>2412</v>
       </c>
-      <c r="D1103" s="8">
-        <v>2.5696E7</v>
-      </c>
+      <c r="D1103" s="8"/>
       <c r="E1103" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34288,7 +34168,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="1104">
+    <row r="1104" hidden="1">
       <c r="A1104" s="6" t="s">
         <v>2416</v>
       </c>
@@ -34298,9 +34178,7 @@
       <c r="C1104" s="7" t="s">
         <v>2417</v>
       </c>
-      <c r="D1104" s="8">
-        <v>2.56344E7</v>
-      </c>
+      <c r="D1104" s="8"/>
       <c r="E1104" s="6" t="s">
         <v>1608</v>
       </c>
@@ -34317,7 +34195,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="1105">
+    <row r="1105" hidden="1">
       <c r="A1105" s="6" t="s">
         <v>2420</v>
       </c>
@@ -34327,9 +34205,7 @@
       <c r="C1105" s="7" t="s">
         <v>2421</v>
       </c>
-      <c r="D1105" s="8">
-        <v>2.53506E7</v>
-      </c>
+      <c r="D1105" s="8"/>
       <c r="E1105" s="6" t="s">
         <v>1608</v>
       </c>
@@ -39183,32 +39059,11 @@
   <autoFilter ref="$A$1:$I$1500">
     <filterColumn colId="2">
       <filters>
-        <filter val="1001630"/>
-        <filter val="1001622"/>
-        <filter val="30500200000"/>
-        <filter val="1000501"/>
-        <filter val="1001822"/>
-        <filter val="1001619"/>
-        <filter val="1001849"/>
-        <filter val="1001846"/>
-        <filter val="30300300000"/>
-        <filter val="1001698"/>
-        <filter val="30310800000"/>
-        <filter val="1001201"/>
-        <filter val="1001294"/>
-        <filter val="1001052"/>
-        <filter val="1001925"/>
-        <filter val="1001927"/>
-        <filter val="1001757"/>
-        <filter val="1001762"/>
-        <filter val="30501400000"/>
-        <filter val="1001717"/>
-        <filter val="30406100000"/>
-        <filter val="1001725"/>
-        <filter val="30602400000"/>
-        <filter val="1001326"/>
-        <filter val="1001199"/>
-        <filter val="30501600000"/>
+        <filter val="1001453"/>
+        <filter val="1001459"/>
+        <filter val="1107376682"/>
+        <filter val="1000826"/>
+        <filter val="1001903"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -39550,15 +39405,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="1">
@@ -39571,10 +39426,10 @@
     </row>
     <row r="5" ht="33.0" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" ht="33.0" customHeight="1">
@@ -39590,12 +39445,12 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
@@ -39606,23 +39461,23 @@
         <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="33.0" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -73,10 +73,13 @@
     <t>نمایش محصول</t>
   </si>
   <si>
+    <t>برند</t>
+  </si>
+  <si>
     <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
   </si>
   <si>
-    <t>برند</t>
+    <t>کد محصول</t>
   </si>
   <si>
     <t>موجود کردن</t>
@@ -85,7 +88,7 @@
     <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
   </si>
   <si>
-    <t>کد محصول</t>
+    <t>قیمت نقد</t>
   </si>
   <si>
     <t>ناموجود کردن</t>
@@ -100,30 +103,45 @@
     <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
   </si>
   <si>
-    <t>قیمت نقد</t>
+    <t>دسته‌بندی</t>
   </si>
   <si>
     <t>عکس محصول</t>
   </si>
   <si>
+    <t>توضیحات</t>
+  </si>
+  <si>
     <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
   </si>
   <si>
-    <t>توضیحات</t>
+    <t>عکس</t>
+  </si>
+  <si>
+    <t>دسته‌بندی اصلی</t>
   </si>
   <si>
     <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
   </si>
   <si>
+    <t>گروه اصلی</t>
+  </si>
+  <si>
     <t>آرایشی و بهداشتی</t>
   </si>
   <si>
-    <t>دسته‌بندی</t>
-  </si>
-  <si>
     <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
   </si>
   <si>
+    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
+  </si>
+  <si>
+    <t>اپل</t>
+  </si>
+  <si>
+    <t>1109410629</t>
+  </si>
+  <si>
     <t>دسته‌بندی‌های مجاز</t>
   </si>
   <si>
@@ -136,28 +154,10 @@
     <t>Product</t>
   </si>
   <si>
-    <t>عکس</t>
-  </si>
-  <si>
     <t>پوشه بنرها</t>
   </si>
   <si>
     <t>baner</t>
-  </si>
-  <si>
-    <t>دسته‌بندی اصلی</t>
-  </si>
-  <si>
-    <t>گروه اصلی</t>
-  </si>
-  <si>
-    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
-  </si>
-  <si>
-    <t>اپل</t>
-  </si>
-  <si>
-    <t>1109410629</t>
   </si>
   <si>
     <t>موبایل</t>
@@ -8048,39 +8048,39 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="6" t="s">
@@ -8102,7 +8102,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>36</v>
@@ -8129,7 +8129,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>39</v>
@@ -8154,7 +8154,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>42</v>
@@ -8177,7 +8177,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>44</v>
@@ -8204,7 +8204,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>48</v>
@@ -8231,7 +8231,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>50</v>
@@ -8258,7 +8258,7 @@
         <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>52</v>
@@ -8287,7 +8287,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>54</v>
@@ -8314,7 +8314,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>56</v>
@@ -8339,7 +8339,7 @@
         <v>57</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>58</v>
@@ -8362,7 +8362,7 @@
         <v>59</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>60</v>
@@ -8387,7 +8387,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>62</v>
@@ -8410,7 +8410,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>64</v>
@@ -8433,7 +8433,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>66</v>
@@ -8458,7 +8458,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>68</v>
@@ -8481,7 +8481,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>70</v>
@@ -8506,7 +8506,7 @@
         <v>71</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>72</v>
@@ -8529,7 +8529,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>74</v>
@@ -8552,7 +8552,7 @@
         <v>75</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>76</v>
@@ -8575,7 +8575,7 @@
         <v>77</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>78</v>
@@ -8598,7 +8598,7 @@
         <v>79</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>80</v>
@@ -8621,7 +8621,7 @@
         <v>81</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>82</v>
@@ -8644,7 +8644,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>84</v>
@@ -8667,7 +8667,7 @@
         <v>85</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>86</v>
@@ -8690,7 +8690,7 @@
         <v>87</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>88</v>
@@ -8713,7 +8713,7 @@
         <v>89</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>90</v>
@@ -8736,7 +8736,7 @@
         <v>91</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>92</v>
@@ -8759,7 +8759,7 @@
         <v>93</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>94</v>
@@ -8782,7 +8782,7 @@
         <v>95</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>96</v>
@@ -8805,7 +8805,7 @@
         <v>97</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>98</v>
@@ -8828,7 +8828,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>100</v>
@@ -8851,7 +8851,7 @@
         <v>101</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>102</v>
@@ -8874,7 +8874,7 @@
         <v>103</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>104</v>
@@ -8897,7 +8897,7 @@
         <v>105</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>106</v>
@@ -8920,7 +8920,7 @@
         <v>107</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>108</v>
@@ -8943,7 +8943,7 @@
         <v>109</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>110</v>
@@ -8966,7 +8966,7 @@
         <v>111</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>112</v>
@@ -8989,7 +8989,7 @@
         <v>113</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>114</v>
@@ -9012,7 +9012,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>116</v>
@@ -9035,7 +9035,7 @@
         <v>117</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>118</v>
@@ -9058,7 +9058,7 @@
         <v>119</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>120</v>
@@ -9081,7 +9081,7 @@
         <v>121</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>122</v>
@@ -9104,7 +9104,7 @@
         <v>123</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>124</v>
@@ -9127,7 +9127,7 @@
         <v>125</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>126</v>
@@ -9150,7 +9150,7 @@
         <v>127</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>128</v>
@@ -9173,7 +9173,7 @@
         <v>129</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>130</v>
@@ -9196,7 +9196,7 @@
         <v>131</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>132</v>
@@ -9219,7 +9219,7 @@
         <v>133</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>134</v>
@@ -9242,7 +9242,7 @@
         <v>135</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>136</v>
@@ -9265,7 +9265,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>138</v>
@@ -9288,7 +9288,7 @@
         <v>139</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>140</v>
@@ -9311,7 +9311,7 @@
         <v>141</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>142</v>
@@ -9334,7 +9334,7 @@
         <v>143</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>144</v>
@@ -9357,7 +9357,7 @@
         <v>145</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>146</v>
@@ -9380,7 +9380,7 @@
         <v>147</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>148</v>
@@ -9405,7 +9405,7 @@
         <v>149</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>150</v>
@@ -9430,7 +9430,7 @@
         <v>151</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>152</v>
@@ -9455,7 +9455,7 @@
         <v>153</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>154</v>
@@ -9480,7 +9480,7 @@
         <v>155</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>156</v>
@@ -9505,7 +9505,7 @@
         <v>157</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>158</v>
@@ -9530,7 +9530,7 @@
         <v>159</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>160</v>
@@ -9555,7 +9555,7 @@
         <v>161</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>162</v>
@@ -9580,7 +9580,7 @@
         <v>163</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>164</v>
@@ -9605,7 +9605,7 @@
         <v>165</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>166</v>
@@ -9628,7 +9628,7 @@
         <v>169</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>170</v>
@@ -9651,7 +9651,7 @@
         <v>171</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>172</v>
@@ -9676,7 +9676,7 @@
         <v>174</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>175</v>
@@ -9701,7 +9701,7 @@
         <v>174</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>178</v>
@@ -9726,7 +9726,7 @@
         <v>179</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>180</v>
@@ -9751,7 +9751,7 @@
         <v>182</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>183</v>
@@ -9774,7 +9774,7 @@
         <v>184</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>185</v>
@@ -9799,7 +9799,7 @@
         <v>174</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>186</v>
@@ -9824,7 +9824,7 @@
         <v>187</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>188</v>
@@ -9849,7 +9849,7 @@
         <v>189</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>190</v>
@@ -9867,7 +9867,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77">
       <c r="A77" s="5" t="s">
         <v>191</v>
       </c>
@@ -9877,7 +9877,9 @@
       <c r="C77" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D77" s="11"/>
+      <c r="D77" s="8">
+        <v>2.02382E8</v>
+      </c>
       <c r="E77" s="6" t="s">
         <v>33</v>
       </c>
@@ -18831,7 +18833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="463" hidden="1">
+    <row r="463">
       <c r="A463" s="6" t="s">
         <v>983</v>
       </c>
@@ -18841,7 +18843,9 @@
       <c r="C463" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="D463" s="8"/>
+      <c r="D463" s="8">
+        <v>3389000.0</v>
+      </c>
       <c r="E463" s="6" t="s">
         <v>33</v>
       </c>
@@ -18885,7 +18889,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="465" hidden="1">
+    <row r="465">
       <c r="A465" s="6" t="s">
         <v>989</v>
       </c>
@@ -18895,7 +18899,9 @@
       <c r="C465" s="7" t="s">
         <v>990</v>
       </c>
-      <c r="D465" s="8"/>
+      <c r="D465" s="8">
+        <v>7853000.0</v>
+      </c>
       <c r="E465" s="6" t="s">
         <v>33</v>
       </c>
@@ -18912,7 +18918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="466" hidden="1">
+    <row r="466">
       <c r="A466" s="6" t="s">
         <v>991</v>
       </c>
@@ -18922,7 +18928,9 @@
       <c r="C466" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="D466" s="8"/>
+      <c r="D466" s="8">
+        <v>4350000.0</v>
+      </c>
       <c r="E466" s="6" t="s">
         <v>33</v>
       </c>
@@ -24415,7 +24423,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="703" hidden="1">
+    <row r="703">
       <c r="A703" s="6" t="s">
         <v>1511</v>
       </c>
@@ -24425,7 +24433,9 @@
       <c r="C703" s="7" t="s">
         <v>1512</v>
       </c>
-      <c r="D703" s="8"/>
+      <c r="D703" s="8">
+        <v>4406000.0</v>
+      </c>
       <c r="E703" s="6" t="s">
         <v>33</v>
       </c>
@@ -24643,7 +24653,7 @@
         <v>1532</v>
       </c>
       <c r="B712" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C712" s="7" t="s">
         <v>1533</v>
@@ -24670,7 +24680,7 @@
         <v>1536</v>
       </c>
       <c r="B713" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C713" s="7" t="s">
         <v>1537</v>
@@ -24697,7 +24707,7 @@
         <v>1538</v>
       </c>
       <c r="B714" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C714" s="7" t="s">
         <v>1539</v>
@@ -24724,7 +24734,7 @@
         <v>1540</v>
       </c>
       <c r="B715" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C715" s="7" t="s">
         <v>1541</v>
@@ -24747,7 +24757,7 @@
         <v>1542</v>
       </c>
       <c r="B716" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C716" s="7" t="s">
         <v>1543</v>
@@ -24770,7 +24780,7 @@
         <v>1544</v>
       </c>
       <c r="B717" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C717" s="7" t="s">
         <v>1545</v>
@@ -24793,7 +24803,7 @@
         <v>1546</v>
       </c>
       <c r="B718" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C718" s="7" t="s">
         <v>1547</v>
@@ -24818,7 +24828,7 @@
         <v>1548</v>
       </c>
       <c r="B719" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C719" s="7" t="s">
         <v>1549</v>
@@ -24843,7 +24853,7 @@
         <v>1550</v>
       </c>
       <c r="B720" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C720" s="7" t="s">
         <v>1551</v>
@@ -24868,7 +24878,7 @@
         <v>1552</v>
       </c>
       <c r="B721" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C721" s="7" t="s">
         <v>1553</v>
@@ -24891,7 +24901,7 @@
         <v>1554</v>
       </c>
       <c r="B722" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C722" s="7" t="s">
         <v>1555</v>
@@ -24914,7 +24924,7 @@
         <v>1556</v>
       </c>
       <c r="B723" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C723" s="7" t="s">
         <v>1557</v>
@@ -24937,7 +24947,7 @@
         <v>1558</v>
       </c>
       <c r="B724" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C724" s="7" t="s">
         <v>1559</v>
@@ -24960,7 +24970,7 @@
         <v>1560</v>
       </c>
       <c r="B725" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C725" s="7" t="s">
         <v>1561</v>
@@ -24983,7 +24993,7 @@
         <v>1562</v>
       </c>
       <c r="B726" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C726" s="7" t="s">
         <v>1563</v>
@@ -25006,7 +25016,7 @@
         <v>1564</v>
       </c>
       <c r="B727" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C727" s="7" t="s">
         <v>1565</v>
@@ -25029,7 +25039,7 @@
         <v>1566</v>
       </c>
       <c r="B728" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C728" s="7" t="s">
         <v>1567</v>
@@ -25052,7 +25062,7 @@
         <v>1568</v>
       </c>
       <c r="B729" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C729" s="7" t="s">
         <v>1569</v>
@@ -25075,7 +25085,7 @@
         <v>1570</v>
       </c>
       <c r="B730" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C730" s="7" t="s">
         <v>1571</v>
@@ -25098,7 +25108,7 @@
         <v>1572</v>
       </c>
       <c r="B731" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C731" s="7" t="s">
         <v>1573</v>
@@ -25125,7 +25135,7 @@
         <v>1574</v>
       </c>
       <c r="B732" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C732" s="7" t="s">
         <v>1575</v>
@@ -25152,7 +25162,7 @@
         <v>1578</v>
       </c>
       <c r="B733" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C733" s="7" t="s">
         <v>1579</v>
@@ -25177,7 +25187,7 @@
         <v>1580</v>
       </c>
       <c r="B734" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C734" s="7" t="s">
         <v>1581</v>
@@ -25200,7 +25210,7 @@
         <v>1582</v>
       </c>
       <c r="B735" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C735" s="7" t="s">
         <v>1583</v>
@@ -25225,7 +25235,7 @@
         <v>1584</v>
       </c>
       <c r="B736" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C736" s="7" t="s">
         <v>1585</v>
@@ -25248,7 +25258,7 @@
         <v>1586</v>
       </c>
       <c r="B737" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C737" s="7" t="s">
         <v>1587</v>
@@ -25271,7 +25281,7 @@
         <v>1588</v>
       </c>
       <c r="B738" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C738" s="7" t="s">
         <v>1589</v>
@@ -25294,7 +25304,7 @@
         <v>1590</v>
       </c>
       <c r="B739" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C739" s="7" t="s">
         <v>1591</v>
@@ -25319,7 +25329,7 @@
         <v>1592</v>
       </c>
       <c r="B740" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C740" s="7" t="s">
         <v>1593</v>
@@ -25344,7 +25354,7 @@
         <v>1594</v>
       </c>
       <c r="B741" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C741" s="7" t="s">
         <v>1595</v>
@@ -25369,7 +25379,7 @@
         <v>1596</v>
       </c>
       <c r="B742" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C742" s="7" t="s">
         <v>1597</v>
@@ -25394,7 +25404,7 @@
         <v>1598</v>
       </c>
       <c r="B743" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C743" s="7" t="s">
         <v>1599</v>
@@ -25419,7 +25429,7 @@
         <v>1600</v>
       </c>
       <c r="B744" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C744" s="7" t="s">
         <v>1601</v>
@@ -28321,7 +28331,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="865" hidden="1">
+    <row r="865">
       <c r="A865" s="5" t="s">
         <v>589</v>
       </c>
@@ -28331,7 +28341,9 @@
       <c r="C865" s="7" t="s">
         <v>1854</v>
       </c>
-      <c r="D865" s="8"/>
+      <c r="D865" s="8">
+        <v>1.17519E8</v>
+      </c>
       <c r="E865" s="6" t="s">
         <v>33</v>
       </c>
@@ -28542,7 +28554,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="874" hidden="1">
+    <row r="874">
       <c r="A874" s="5" t="s">
         <v>1873</v>
       </c>
@@ -28552,7 +28564,9 @@
       <c r="C874" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="D874" s="8"/>
+      <c r="D874" s="8">
+        <v>8.8139E7</v>
+      </c>
       <c r="E874" s="6" t="s">
         <v>33</v>
       </c>
@@ -28698,7 +28712,9 @@
       <c r="C880" s="7" t="s">
         <v>1885</v>
       </c>
-      <c r="D880" s="8"/>
+      <c r="D880" s="8">
+        <v>1.55939E8</v>
+      </c>
       <c r="E880" s="6" t="s">
         <v>33</v>
       </c>
@@ -28750,7 +28766,9 @@
       <c r="C882" s="7" t="s">
         <v>1889</v>
       </c>
-      <c r="D882" s="8"/>
+      <c r="D882" s="8">
+        <v>1.24299E8</v>
+      </c>
       <c r="E882" s="6" t="s">
         <v>33</v>
       </c>
@@ -29230,7 +29248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="902" hidden="1">
+    <row r="902">
       <c r="A902" s="5" t="s">
         <v>768</v>
       </c>
@@ -29240,7 +29258,9 @@
       <c r="C902" s="7" t="s">
         <v>1937</v>
       </c>
-      <c r="D902" s="8"/>
+      <c r="D902" s="8">
+        <v>8.5879E7</v>
+      </c>
       <c r="E902" s="6" t="s">
         <v>33</v>
       </c>
@@ -30981,7 +31001,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="977" hidden="1">
+    <row r="977">
       <c r="A977" s="5" t="s">
         <v>872</v>
       </c>
@@ -30991,7 +31011,9 @@
       <c r="C977" s="7" t="s">
         <v>2106</v>
       </c>
-      <c r="D977" s="11"/>
+      <c r="D977" s="8">
+        <v>6.7799E7</v>
+      </c>
       <c r="E977" s="6" t="s">
         <v>33</v>
       </c>
@@ -31121,7 +31143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="983" hidden="1">
+    <row r="983">
       <c r="A983" s="5" t="s">
         <v>2117</v>
       </c>
@@ -31131,7 +31153,9 @@
       <c r="C983" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="D983" s="8"/>
+      <c r="D983" s="8">
+        <v>8.8139E7</v>
+      </c>
       <c r="E983" s="6" t="s">
         <v>33</v>
       </c>
@@ -31844,7 +31868,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="1012" hidden="1">
+    <row r="1012">
       <c r="A1012" s="6" t="s">
         <v>2198</v>
       </c>
@@ -31854,7 +31878,9 @@
       <c r="C1012" s="7" t="s">
         <v>2199</v>
       </c>
-      <c r="D1012" s="8"/>
+      <c r="D1012" s="8">
+        <v>3615000.0</v>
+      </c>
       <c r="E1012" s="6" t="s">
         <v>33</v>
       </c>
@@ -31871,7 +31897,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="1013" hidden="1">
+    <row r="1013">
       <c r="A1013" s="6" t="s">
         <v>2200</v>
       </c>
@@ -31881,7 +31907,9 @@
       <c r="C1013" s="7" t="s">
         <v>2201</v>
       </c>
-      <c r="D1013" s="8"/>
+      <c r="D1013" s="8">
+        <v>4745000.0</v>
+      </c>
       <c r="E1013" s="6" t="s">
         <v>33</v>
       </c>
@@ -31898,7 +31926,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="1014" hidden="1">
+    <row r="1014">
       <c r="A1014" s="6" t="s">
         <v>2202</v>
       </c>
@@ -31908,7 +31936,9 @@
       <c r="C1014" s="7" t="s">
         <v>2203</v>
       </c>
-      <c r="D1014" s="8"/>
+      <c r="D1014" s="8">
+        <v>8135000.0</v>
+      </c>
       <c r="E1014" s="6" t="s">
         <v>33</v>
       </c>
@@ -33248,7 +33278,7 @@
         <v>2321</v>
       </c>
       <c r="B1067" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C1067" s="7" t="s">
         <v>2322</v>
@@ -33626,7 +33656,7 @@
         <v>2353</v>
       </c>
       <c r="B1083" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C1083" s="7" t="s">
         <v>2354</v>
@@ -39059,11 +39089,24 @@
   <autoFilter ref="$A$1:$I$1500">
     <filterColumn colId="2">
       <filters>
+        <filter val="1105995030"/>
+        <filter val="1104533241"/>
         <filter val="1001453"/>
         <filter val="1001459"/>
+        <filter val="1000598"/>
+        <filter val="1001449"/>
         <filter val="1107376682"/>
+        <filter val="1104377131"/>
+        <filter val="1001020"/>
         <filter val="1000826"/>
         <filter val="1001903"/>
+        <filter val="1001774"/>
+        <filter val="1001770"/>
+        <filter val="1001772"/>
+        <filter val="1001538"/>
+        <filter val="1001362"/>
+        <filter val="1107825176"/>
+        <filter val="1001007934"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -39405,39 +39448,39 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="33.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="33.0" customHeight="1">
@@ -39445,39 +39488,39 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="33.0" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="33.0" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -61,15 +61,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6240" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6243" uniqueCount="1439">
+  <si>
+    <t>نام محصول</t>
+  </si>
   <si>
     <t>موضوع</t>
   </si>
   <si>
+    <t>برند</t>
+  </si>
+  <si>
     <t>کد کالا</t>
   </si>
   <si>
-    <t>نام محصول</t>
+    <t>کد محصول</t>
+  </si>
+  <si>
+    <t>قیمت نقد</t>
   </si>
   <si>
     <t>راهنما</t>
@@ -81,55 +90,52 @@
     <t>قیمت فروش ( ریال )</t>
   </si>
   <si>
-    <t>برند</t>
+    <t>دسته‌بندی</t>
+  </si>
+  <si>
+    <t>توضیحات</t>
   </si>
   <si>
     <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
   </si>
   <si>
-    <t>کد محصول</t>
+    <t>عکس</t>
   </si>
   <si>
     <t>موجود کردن</t>
   </si>
   <si>
+    <t>دسته‌بندی اصلی</t>
+  </si>
+  <si>
+    <t>گروه اصلی</t>
+  </si>
+  <si>
     <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
   </si>
   <si>
-    <t>قیمت نقد</t>
-  </si>
-  <si>
     <t>ناموجود کردن</t>
   </si>
   <si>
     <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
   </si>
   <si>
+    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
+  </si>
+  <si>
     <t>فهرست برندها</t>
   </si>
   <si>
-    <t>دسته‌بندی</t>
-  </si>
-  <si>
     <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
   </si>
   <si>
-    <t>توضیحات</t>
-  </si>
-  <si>
     <t>عکس محصول</t>
   </si>
   <si>
     <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
   </si>
   <si>
-    <t>عکس</t>
-  </si>
-  <si>
-    <t>دسته‌بندی اصلی</t>
-  </si>
-  <si>
-    <t>گروه اصلی</t>
+    <t>اپل</t>
   </si>
   <si>
     <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
@@ -141,16 +147,10 @@
     <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
   </si>
   <si>
-    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
-  </si>
-  <si>
     <t>دسته‌بندی‌های مجاز</t>
   </si>
   <si>
     <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
-  </si>
-  <si>
-    <t>اپل</t>
   </si>
   <si>
     <t>پوشه عکس محصولات</t>
@@ -4315,8 +4315,7 @@
     <t>دیپوینت</t>
   </si>
   <si>
-    <t xml:space="preserve">ارتفاع 190، پهنای 86 و عمق 77 سانتی متر، میزان مصرف انرژی +A، دارای 3 طبقه در یخچال و 3 کشو در فریزر، دارای سیستم نوفراست، ۴۲۷ لیتر
-</t>
+    <t>ارتفاع 190، پهنای 86 و عمق 77 سانتی متر، میزان مصرف انرژی +A، دارای 3 طبقه در یخچال و 3 کشو در فریزر، دارای سیستم نوفراست، ۴۲۷ لیتر، سفید / نقره ای</t>
   </si>
   <si>
     <t>یخچال فریزر</t>
@@ -4328,7 +4327,13 @@
     <t>یخچال فریزر ساید بای ساید اتوماتیک سفید دیپوینت مدل INSIDER-W</t>
   </si>
   <si>
+    <t>ارتفاع 180، پهنای 92 و عمق 74 سانتی متر، میزان مصرف انرژی B، دارای 4 طبقه و 2 کشو در یخچال، ۳۹۳ لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
     <t>یخچال فریزر ساید بای ساید اتوماتیک نقره ای دیپوینت مدل INSIDER-S</t>
+  </si>
+  <si>
+    <t>ارتفاع 180، پهنای 92 و عمق 74 سانتی متر، میزان مصرف انرژی B، دارای 4 طبقه و 2 کشو در فریزر، ۳۹۳ لیتر، سفید / نقره ای</t>
   </si>
   <si>
     <t>یخچال سفید دیپوینت دوقلو مدل D5i-W</t>
@@ -4484,22 +4489,22 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
@@ -4791,40 +4796,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" s="10">
         <v>1.109410629E9</v>
@@ -4852,7 +4857,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C3" s="10">
         <v>1.102420474E9</v>
@@ -4882,7 +4887,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10">
         <v>1.108767131E9</v>
@@ -4910,7 +4915,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10">
         <v>1.108513754E9</v>
@@ -4936,7 +4941,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C6" s="10">
         <v>1.103961018E9</v>
@@ -4966,7 +4971,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10">
         <v>1.109795907E9</v>
@@ -4996,7 +5001,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10">
         <v>1.107343129E9</v>
@@ -5026,7 +5031,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="10">
         <v>1.107376682E9</v>
@@ -5056,7 +5061,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10">
         <v>1.101106336E9</v>
@@ -5086,7 +5091,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="10">
         <v>1.104186523E9</v>
@@ -5114,7 +5119,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" s="10">
         <v>1.10473176E9</v>
@@ -5140,7 +5145,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" s="10">
         <v>1.109650453E9</v>
@@ -5168,7 +5173,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" s="10">
         <v>1.10808351E9</v>
@@ -5194,7 +5199,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C15" s="10">
         <v>1.109487106E9</v>
@@ -5220,7 +5225,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C16" s="10">
         <v>1.109460131E9</v>
@@ -5248,7 +5253,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C17" s="10">
         <v>1.105617587E9</v>
@@ -5274,7 +5279,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C18" s="10">
         <v>1.106819388E9</v>
@@ -5302,7 +5307,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C19" s="10">
         <v>1.001004778E9</v>
@@ -5328,7 +5333,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C20" s="10">
         <v>1.00100478E9</v>
@@ -5354,7 +5359,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C21" s="10">
         <v>1.001004782E9</v>
@@ -5380,7 +5385,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
         <v>1.001004784E9</v>
@@ -5406,7 +5411,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C23" s="10">
         <v>1.104349913E9</v>
@@ -5432,7 +5437,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="10">
         <v>1.109587805E9</v>
@@ -5458,7 +5463,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C25" s="10">
         <v>1.107699532E9</v>
@@ -5484,7 +5489,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
         <v>1.107648299E9</v>
@@ -5510,7 +5515,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C27" s="10">
         <v>1.109287401E9</v>
@@ -5536,7 +5541,7 @@
         <v>65</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C28" s="10">
         <v>1.001004781E9</v>
@@ -5562,7 +5567,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C29" s="10">
         <v>1.001021394E9</v>
@@ -5588,7 +5593,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C30" s="10">
         <v>1.001021393E9</v>
@@ -5614,7 +5619,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C31" s="10">
         <v>1.001021391E9</v>
@@ -5640,7 +5645,7 @@
         <v>69</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C32" s="10">
         <v>1.001021395E9</v>
@@ -5666,7 +5671,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C33" s="10">
         <v>1.001021392E9</v>
@@ -5692,7 +5697,7 @@
         <v>71</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C34" s="10">
         <v>1.001006153E9</v>
@@ -5718,7 +5723,7 @@
         <v>72</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C35" s="10">
         <v>1.001010412E9</v>
@@ -5744,7 +5749,7 @@
         <v>73</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C36" s="10">
         <v>1.001006156E9</v>
@@ -5770,7 +5775,7 @@
         <v>74</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C37" s="10">
         <v>1.001006157E9</v>
@@ -5796,7 +5801,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C38" s="10">
         <v>1.001006158E9</v>
@@ -5822,7 +5827,7 @@
         <v>76</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C39" s="10">
         <v>1.001001379E9</v>
@@ -5848,7 +5853,7 @@
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C40" s="10">
         <v>1.001001377E9</v>
@@ -5874,7 +5879,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C41" s="10">
         <v>1.001005247E9</v>
@@ -5900,7 +5905,7 @@
         <v>79</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C42" s="10">
         <v>1.001001378E9</v>
@@ -5926,7 +5931,7 @@
         <v>80</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C43" s="10">
         <v>1.00100138E9</v>
@@ -5952,7 +5957,7 @@
         <v>81</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C44" s="10">
         <v>1.001005248E9</v>
@@ -5978,7 +5983,7 @@
         <v>82</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C45" s="10">
         <v>1.001001381E9</v>
@@ -6004,7 +6009,7 @@
         <v>83</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C46" s="10">
         <v>1.001005249E9</v>
@@ -6030,7 +6035,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C47" s="10">
         <v>1.101902167E9</v>
@@ -6056,7 +6061,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C48" s="10">
         <v>1.10476745E9</v>
@@ -6082,7 +6087,7 @@
         <v>86</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C49" s="10">
         <v>1.107951155E9</v>
@@ -6108,7 +6113,7 @@
         <v>87</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C50" s="10">
         <v>1.103162512E9</v>
@@ -6134,7 +6139,7 @@
         <v>88</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C51" s="10">
         <v>1.101210104E9</v>
@@ -6160,7 +6165,7 @@
         <v>89</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C52" s="10">
         <v>1.102684171E9</v>
@@ -6186,7 +6191,7 @@
         <v>90</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C53" s="10">
         <v>1.106756931E9</v>
@@ -6212,7 +6217,7 @@
         <v>91</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C54" s="10">
         <v>1.105904445E9</v>
@@ -6238,7 +6243,7 @@
         <v>92</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C55" s="10">
         <v>1.101567826E9</v>
@@ -6264,7 +6269,7 @@
         <v>93</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C56" s="10">
         <v>1.101372157E9</v>
@@ -6290,7 +6295,7 @@
         <v>94</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C57" s="10">
         <v>1.101198832E9</v>
@@ -6318,7 +6323,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C58" s="10">
         <v>1.105747685E9</v>
@@ -6346,7 +6351,7 @@
         <v>96</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C59" s="10">
         <v>1.102034608E9</v>
@@ -6374,7 +6379,7 @@
         <v>97</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C60" s="10">
         <v>1.106909378E9</v>
@@ -6402,7 +6407,7 @@
         <v>98</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C61" s="10">
         <v>1.106425921E9</v>
@@ -6430,7 +6435,7 @@
         <v>99</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C62" s="10">
         <v>1.10938833E9</v>
@@ -6458,7 +6463,7 @@
         <v>100</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C63" s="10">
         <v>1.10626332E9</v>
@@ -6486,7 +6491,7 @@
         <v>101</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C64" s="10">
         <v>1.101786232E9</v>
@@ -6514,7 +6519,7 @@
         <v>102</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C65" s="10">
         <v>1.103047943E9</v>
@@ -6542,7 +6547,7 @@
         <v>103</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C66" s="10">
         <v>1.001011708E9</v>
@@ -6568,7 +6573,7 @@
         <v>106</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C67" s="10">
         <v>1.001011816E9</v>
@@ -6594,7 +6599,7 @@
         <v>107</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C68" s="10">
         <v>1.001021157E9</v>
@@ -6622,7 +6627,7 @@
         <v>109</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C69" s="10">
         <v>1.001012566E9</v>
@@ -6650,7 +6655,7 @@
         <v>109</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C70" s="10">
         <v>1.001012092E9</v>
@@ -6678,7 +6683,7 @@
         <v>112</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C71" s="10">
         <v>1.001020005E9</v>
@@ -6706,7 +6711,7 @@
         <v>114</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C72" s="10">
         <v>1.102722242E9</v>
@@ -6732,7 +6737,7 @@
         <v>115</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C73" s="10">
         <v>1.001021166E9</v>
@@ -6760,7 +6765,7 @@
         <v>109</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C74" s="10">
         <v>1.001011734E9</v>
@@ -6788,7 +6793,7 @@
         <v>116</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C75" s="10">
         <v>1.001020003E9</v>
@@ -6816,7 +6821,7 @@
         <v>117</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C76" s="10">
         <v>1.001007259E9</v>
@@ -23518,7 +23523,7 @@
         <v>824</v>
       </c>
       <c r="B712" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C712" s="10">
         <v>1001687.0</v>
@@ -23548,7 +23553,7 @@
         <v>827</v>
       </c>
       <c r="B713" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C713" s="10">
         <v>1000343.0</v>
@@ -23578,7 +23583,7 @@
         <v>828</v>
       </c>
       <c r="B714" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C714" s="10">
         <v>1000345.0</v>
@@ -23608,7 +23613,7 @@
         <v>829</v>
       </c>
       <c r="B715" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C715" s="10">
         <v>1001634.0</v>
@@ -23634,7 +23639,7 @@
         <v>830</v>
       </c>
       <c r="B716" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C716" s="10">
         <v>1001635.0</v>
@@ -23660,7 +23665,7 @@
         <v>831</v>
       </c>
       <c r="B717" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C717" s="10">
         <v>1001636.0</v>
@@ -23686,7 +23691,7 @@
         <v>832</v>
       </c>
       <c r="B718" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C718" s="10">
         <v>1001527.0</v>
@@ -23714,7 +23719,7 @@
         <v>833</v>
       </c>
       <c r="B719" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C719" s="10">
         <v>1001526.0</v>
@@ -23742,7 +23747,7 @@
         <v>834</v>
       </c>
       <c r="B720" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C720" s="10">
         <v>1001525.0</v>
@@ -23770,7 +23775,7 @@
         <v>835</v>
       </c>
       <c r="B721" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C721" s="10">
         <v>1000222.0</v>
@@ -23796,7 +23801,7 @@
         <v>836</v>
       </c>
       <c r="B722" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C722" s="10">
         <v>1000223.0</v>
@@ -23822,7 +23827,7 @@
         <v>837</v>
       </c>
       <c r="B723" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C723" s="10">
         <v>1000224.0</v>
@@ -23848,7 +23853,7 @@
         <v>838</v>
       </c>
       <c r="B724" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C724" s="10">
         <v>1000225.0</v>
@@ -23874,7 +23879,7 @@
         <v>839</v>
       </c>
       <c r="B725" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C725" s="10">
         <v>1001237.0</v>
@@ -23900,7 +23905,7 @@
         <v>840</v>
       </c>
       <c r="B726" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C726" s="10">
         <v>1001236.0</v>
@@ -23926,7 +23931,7 @@
         <v>841</v>
       </c>
       <c r="B727" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C727" s="10">
         <v>1000227.0</v>
@@ -23952,7 +23957,7 @@
         <v>842</v>
       </c>
       <c r="B728" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C728" s="10">
         <v>1000228.0</v>
@@ -23978,7 +23983,7 @@
         <v>843</v>
       </c>
       <c r="B729" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C729" s="10">
         <v>1000229.0</v>
@@ -24004,7 +24009,7 @@
         <v>844</v>
       </c>
       <c r="B730" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C730" s="10">
         <v>1000230.0</v>
@@ -24030,7 +24035,7 @@
         <v>845</v>
       </c>
       <c r="B731" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C731" s="10">
         <v>1000341.0</v>
@@ -24060,7 +24065,7 @@
         <v>846</v>
       </c>
       <c r="B732" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C732" s="10">
         <v>1000674.0</v>
@@ -24090,7 +24095,7 @@
         <v>849</v>
       </c>
       <c r="B733" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C733" s="10">
         <v>1000374.0</v>
@@ -24118,7 +24123,7 @@
         <v>850</v>
       </c>
       <c r="B734" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C734" s="10">
         <v>1001308.0</v>
@@ -24144,7 +24149,7 @@
         <v>851</v>
       </c>
       <c r="B735" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C735" s="10">
         <v>1000242.0</v>
@@ -24172,7 +24177,7 @@
         <v>852</v>
       </c>
       <c r="B736" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C736" s="10">
         <v>1001764.0</v>
@@ -24198,7 +24203,7 @@
         <v>853</v>
       </c>
       <c r="B737" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C737" s="10">
         <v>1001766.0</v>
@@ -24224,7 +24229,7 @@
         <v>854</v>
       </c>
       <c r="B738" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C738" s="10">
         <v>1001768.0</v>
@@ -24250,7 +24255,7 @@
         <v>855</v>
       </c>
       <c r="B739" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C739" s="10">
         <v>1001674.0</v>
@@ -24278,7 +24283,7 @@
         <v>856</v>
       </c>
       <c r="B740" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C740" s="10">
         <v>1001675.0</v>
@@ -24306,7 +24311,7 @@
         <v>857</v>
       </c>
       <c r="B741" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C741" s="10">
         <v>1001677.0</v>
@@ -24334,7 +24339,7 @@
         <v>858</v>
       </c>
       <c r="B742" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C742" s="10">
         <v>1001678.0</v>
@@ -24362,7 +24367,7 @@
         <v>859</v>
       </c>
       <c r="B743" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C743" s="10">
         <v>1001676.0</v>
@@ -24390,7 +24395,7 @@
         <v>860</v>
       </c>
       <c r="B744" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C744" s="10">
         <v>1000240.0</v>
@@ -33192,7 +33197,7 @@
         <v>1261</v>
       </c>
       <c r="B1067" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C1067" s="10">
         <v>3.20127115001E11</v>
@@ -33618,7 +33623,7 @@
         <v>1277</v>
       </c>
       <c r="B1083" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C1083" s="10">
         <v>3.20127115004E11</v>
@@ -35262,7 +35267,9 @@
       <c r="E1139" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1139" s="12"/>
+      <c r="F1139" s="18" t="s">
+        <v>1417</v>
+      </c>
       <c r="G1139" s="12"/>
       <c r="H1139" s="18" t="s">
         <v>1294</v>
@@ -35287,7 +35294,9 @@
       <c r="E1140" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1140" s="12"/>
+      <c r="F1140" s="18" t="s">
+        <v>1421</v>
+      </c>
       <c r="G1140" s="12"/>
       <c r="H1140" s="18" t="s">
         <v>1294</v>
@@ -35298,7 +35307,7 @@
     </row>
     <row r="1141">
       <c r="A1141" s="18" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B1141" s="18" t="s">
         <v>1416</v>
@@ -35312,7 +35321,9 @@
       <c r="E1141" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1141" s="12"/>
+      <c r="F1141" s="18" t="s">
+        <v>1423</v>
+      </c>
       <c r="G1141" s="12"/>
       <c r="H1141" s="18" t="s">
         <v>1294</v>
@@ -35323,7 +35334,7 @@
     </row>
     <row r="1142">
       <c r="A1142" s="18" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B1142" s="18" t="s">
         <v>1416</v>
@@ -35343,12 +35354,12 @@
         <v>1294</v>
       </c>
       <c r="I1142" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" s="18" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B1143" s="18" t="s">
         <v>1416</v>
@@ -35368,12 +35379,12 @@
         <v>1294</v>
       </c>
       <c r="I1143" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" s="18" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B1144" s="18" t="s">
         <v>1416</v>
@@ -35393,12 +35404,12 @@
         <v>1294</v>
       </c>
       <c r="I1144" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" s="18" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B1145" s="18" t="s">
         <v>1416</v>
@@ -35418,12 +35429,12 @@
         <v>1294</v>
       </c>
       <c r="I1145" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" s="18" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B1146" s="18" t="s">
         <v>1416</v>
@@ -35443,12 +35454,12 @@
         <v>1294</v>
       </c>
       <c r="I1146" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" s="18" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B1147" s="18" t="s">
         <v>1416</v>
@@ -35468,12 +35479,12 @@
         <v>1294</v>
       </c>
       <c r="I1147" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" s="18" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B1148" s="18" t="s">
         <v>1416</v>
@@ -35493,12 +35504,12 @@
         <v>1294</v>
       </c>
       <c r="I1148" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" s="18" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B1149" s="18" t="s">
         <v>1416</v>
@@ -35518,12 +35529,12 @@
         <v>1294</v>
       </c>
       <c r="I1149" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" s="18" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B1150" s="18" t="s">
         <v>1416</v>
@@ -35543,12 +35554,12 @@
         <v>1294</v>
       </c>
       <c r="I1150" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" s="18" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B1151" s="18" t="s">
         <v>1416</v>
@@ -35568,12 +35579,12 @@
         <v>1294</v>
       </c>
       <c r="I1151" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="18" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B1152" s="18" t="s">
         <v>1416</v>
@@ -35593,12 +35604,12 @@
         <v>1294</v>
       </c>
       <c r="I1152" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="18" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B1153" s="18" t="s">
         <v>1416</v>
@@ -35618,12 +35629,12 @@
         <v>1294</v>
       </c>
       <c r="I1153" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="18" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B1154" s="18" t="s">
         <v>1416</v>
@@ -35648,7 +35659,7 @@
     </row>
     <row r="1155">
       <c r="A1155" s="18" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B1155" s="18" t="s">
         <v>1416</v>
@@ -39798,15 +39809,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1001687.0</v>
       </c>
       <c r="B2" s="7">
@@ -39814,7 +39825,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>1000341.0</v>
       </c>
       <c r="B3" s="7">
@@ -39822,7 +39833,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1000343.0</v>
       </c>
       <c r="B4" s="7">
@@ -39830,7 +39841,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1000345.0</v>
       </c>
       <c r="B5" s="7">
@@ -39838,7 +39849,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>1000674.0</v>
       </c>
       <c r="B6" s="7">
@@ -39846,7 +39857,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>1001459.0</v>
       </c>
       <c r="B7" s="7">
@@ -39854,7 +39865,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>1001453.0</v>
       </c>
       <c r="B8" s="7">
@@ -39862,7 +39873,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>1001020.0</v>
       </c>
       <c r="B9" s="7">
@@ -39870,7 +39881,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>1000598.0</v>
       </c>
       <c r="B10" s="7">
@@ -39878,7 +39889,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>1001362.0</v>
       </c>
       <c r="B11" s="7">
@@ -39886,7 +39897,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>1001757.0</v>
       </c>
       <c r="B12" s="7">
@@ -39894,7 +39905,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>1001762.0</v>
       </c>
       <c r="B13" s="7">
@@ -39902,7 +39913,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>1000501.0</v>
       </c>
       <c r="B14" s="7">
@@ -39910,7 +39921,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>1001849.0</v>
       </c>
       <c r="B15" s="7">
@@ -39918,7 +39929,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>1001927.0</v>
       </c>
       <c r="B16" s="7">
@@ -39926,7 +39937,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>1001630.0</v>
       </c>
       <c r="B17" s="7">
@@ -39934,7 +39945,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>1001774.0</v>
       </c>
       <c r="B18" s="7">
@@ -39942,7 +39953,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>1001772.0</v>
       </c>
       <c r="B19" s="7">
@@ -39950,7 +39961,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>1001770.0</v>
       </c>
       <c r="B20" s="7">
@@ -39958,7 +39969,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>1001968.0</v>
       </c>
       <c r="B21" s="7">
@@ -39966,7 +39977,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>1001964.0</v>
       </c>
       <c r="B22" s="7">
@@ -39974,7 +39985,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>1001895.0</v>
       </c>
       <c r="B23" s="7">
@@ -39982,7 +39993,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>1001888.0</v>
       </c>
       <c r="B24" s="7">
@@ -39990,7 +40001,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>1001891.0</v>
       </c>
       <c r="B25" s="7">
@@ -39998,7 +40009,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>1001890.0</v>
       </c>
       <c r="B26" s="7">
@@ -40006,7 +40017,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>1001962.0</v>
       </c>
       <c r="B27" s="7">
@@ -40014,7 +40025,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5">
+      <c r="A28" s="6">
         <v>1001960.0</v>
       </c>
       <c r="B28" s="7">
@@ -40022,7 +40033,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5">
+      <c r="A29" s="6">
         <v>1001958.0</v>
       </c>
       <c r="B29" s="7">
@@ -40030,7 +40041,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="6">
         <v>1001957.0</v>
       </c>
       <c r="B30" s="7">
@@ -40038,7 +40049,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="6">
         <v>1001955.0</v>
       </c>
       <c r="B31" s="7">
@@ -40046,7 +40057,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5">
+      <c r="A32" s="6">
         <v>1001952.0</v>
       </c>
       <c r="B32" s="7">
@@ -40054,7 +40065,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>1001951.0</v>
       </c>
       <c r="B33" s="7">
@@ -40062,7 +40073,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>1001884.0</v>
       </c>
       <c r="B34" s="7">
@@ -40070,7 +40081,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>1001885.0</v>
       </c>
       <c r="B35" s="7">
@@ -40078,7 +40089,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>1001867.0</v>
       </c>
       <c r="B36" s="7">
@@ -40086,7 +40097,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>1001868.0</v>
       </c>
       <c r="B37" s="7">
@@ -40094,7 +40105,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>1001622.0</v>
       </c>
       <c r="B38" s="7">
@@ -40102,7 +40113,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>1001680.0</v>
       </c>
       <c r="B39" s="7">
@@ -40110,7 +40121,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>1001326.0</v>
       </c>
       <c r="B40" s="7">
@@ -40118,7 +40129,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>1001294.0</v>
       </c>
       <c r="B41" s="7">
@@ -40126,7 +40137,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>1001698.0</v>
       </c>
       <c r="B42" s="7">
@@ -40134,7 +40145,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>1001725.0</v>
       </c>
       <c r="B43" s="7">
@@ -40142,7 +40153,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>1001717.0</v>
       </c>
       <c r="B44" s="7">
@@ -40150,7 +40161,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>1001822.0</v>
       </c>
       <c r="B45" s="7">
@@ -40158,7 +40169,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>1001846.0</v>
       </c>
       <c r="B46" s="7">
@@ -40166,7 +40177,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>1000282.0</v>
       </c>
       <c r="B47" s="7">
@@ -40174,7 +40185,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5">
+      <c r="A48" s="6">
         <v>1001925.0</v>
       </c>
       <c r="B48" s="7">
@@ -40182,7 +40193,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5">
+      <c r="A49" s="6">
         <v>1001619.0</v>
       </c>
       <c r="B49" s="7">
@@ -40190,7 +40201,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5">
+      <c r="A50" s="6">
         <v>1001201.0</v>
       </c>
       <c r="B50" s="7">
@@ -40198,7 +40209,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5">
+      <c r="A51" s="6">
         <v>1001199.0</v>
       </c>
       <c r="B51" s="7">
@@ -40206,7 +40217,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5">
+      <c r="A52" s="6">
         <v>1.109226956E9</v>
       </c>
       <c r="B52" s="7">
@@ -40214,7 +40225,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5">
+      <c r="A53" s="6">
         <v>1.108040902E9</v>
       </c>
       <c r="B53" s="7">
@@ -40222,7 +40233,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5">
+      <c r="A54" s="6">
         <v>1.105150079E9</v>
       </c>
       <c r="B54" s="7">
@@ -40230,7 +40241,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5">
+      <c r="A55" s="6">
         <v>1.101640902E9</v>
       </c>
       <c r="B55" s="7">
@@ -40238,7 +40249,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5">
+      <c r="A56" s="6">
         <v>1.104647613E9</v>
       </c>
       <c r="B56" s="7">
@@ -40246,7 +40257,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5">
+      <c r="A57" s="6">
         <v>1.102837029E9</v>
       </c>
       <c r="B57" s="7">
@@ -40254,7 +40265,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5">
+      <c r="A58" s="6">
         <v>1.101819678E9</v>
       </c>
       <c r="B58" s="7">
@@ -40262,7 +40273,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5">
+      <c r="A59" s="6">
         <v>1.108735205E9</v>
       </c>
       <c r="B59" s="7">
@@ -40270,7 +40281,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5">
+      <c r="A60" s="6">
         <v>1.109996356E9</v>
       </c>
       <c r="B60" s="7">
@@ -40278,7 +40289,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5">
+      <c r="A61" s="6">
         <v>1.10464317E9</v>
       </c>
       <c r="B61" s="7">
@@ -40286,7 +40297,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5">
+      <c r="A62" s="6">
         <v>1.10967804E9</v>
       </c>
       <c r="B62" s="7">
@@ -40294,7 +40305,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5">
+      <c r="A63" s="6">
         <v>1.103693849E9</v>
       </c>
       <c r="B63" s="7">
@@ -40302,7 +40313,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5">
+      <c r="A64" s="6">
         <v>1.107969437E9</v>
       </c>
       <c r="B64" s="7">
@@ -40310,7 +40321,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5">
+      <c r="A65" s="6">
         <v>1.103854321E9</v>
       </c>
       <c r="B65" s="7">
@@ -40318,7 +40329,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5">
+      <c r="A66" s="6">
         <v>1.105928955E9</v>
       </c>
       <c r="B66" s="7">
@@ -40326,7 +40337,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5">
+      <c r="A67" s="6">
         <v>1.104033685E9</v>
       </c>
       <c r="B67" s="7">
@@ -43161,90 +43172,90 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="33.0" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="33.0" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="33.0" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="33.0" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="33.0" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="33.0" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="33.0" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" ht="33.0" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
     </row>

--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -61,108 +61,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6243" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6269" uniqueCount="1453">
+  <si>
+    <t>موضوع</t>
+  </si>
   <si>
     <t>نام محصول</t>
   </si>
   <si>
-    <t>موضوع</t>
+    <t>کد کالا</t>
+  </si>
+  <si>
+    <t>راهنما</t>
+  </si>
+  <si>
+    <t>نمایش محصول</t>
+  </si>
+  <si>
+    <t>قیمت فروش ( ریال )</t>
+  </si>
+  <si>
+    <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
+  </si>
+  <si>
+    <t>موجود کردن</t>
+  </si>
+  <si>
+    <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
+  </si>
+  <si>
+    <t>ناموجود کردن</t>
+  </si>
+  <si>
+    <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
+  </si>
+  <si>
+    <t>فهرست برندها</t>
+  </si>
+  <si>
+    <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
   </si>
   <si>
     <t>برند</t>
   </si>
   <si>
-    <t>کد کالا</t>
+    <t>عکس محصول</t>
+  </si>
+  <si>
+    <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
   </si>
   <si>
     <t>کد محصول</t>
   </si>
   <si>
+    <t>توضیحات</t>
+  </si>
+  <si>
+    <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
+  </si>
+  <si>
+    <t>آرایشی و بهداشتی</t>
+  </si>
+  <si>
+    <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
+  </si>
+  <si>
+    <t>دسته‌بندی‌های مجاز</t>
+  </si>
+  <si>
     <t>قیمت نقد</t>
   </si>
   <si>
-    <t>راهنما</t>
-  </si>
-  <si>
-    <t>نمایش محصول</t>
-  </si>
-  <si>
-    <t>قیمت فروش ( ریال )</t>
+    <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
+  </si>
+  <si>
+    <t>پوشه عکس محصولات</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>پوشه بنرها</t>
   </si>
   <si>
     <t>دسته‌بندی</t>
   </si>
   <si>
-    <t>توضیحات</t>
-  </si>
-  <si>
-    <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
+    <t>baner</t>
   </si>
   <si>
     <t>عکس</t>
   </si>
   <si>
-    <t>موجود کردن</t>
-  </si>
-  <si>
     <t>دسته‌بندی اصلی</t>
   </si>
   <si>
     <t>گروه اصلی</t>
   </si>
   <si>
-    <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
-  </si>
-  <si>
-    <t>ناموجود کردن</t>
-  </si>
-  <si>
-    <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
-  </si>
-  <si>
     <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
   </si>
   <si>
-    <t>فهرست برندها</t>
-  </si>
-  <si>
-    <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
-  </si>
-  <si>
-    <t>عکس محصول</t>
-  </si>
-  <si>
-    <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
-  </si>
-  <si>
     <t>اپل</t>
-  </si>
-  <si>
-    <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
-  </si>
-  <si>
-    <t>آرایشی و بهداشتی</t>
-  </si>
-  <si>
-    <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
-  </si>
-  <si>
-    <t>دسته‌بندی‌های مجاز</t>
-  </si>
-  <si>
-    <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
-  </si>
-  <si>
-    <t>پوشه عکس محصولات</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>پوشه بنرها</t>
-  </si>
-  <si>
-    <t>baner</t>
   </si>
   <si>
     <t>موبایل</t>
@@ -4318,33 +4318,54 @@
     <t>ارتفاع 190، پهنای 86 و عمق 77 سانتی متر، میزان مصرف انرژی +A، دارای 3 طبقه در یخچال و 3 کشو در فریزر، دارای سیستم نوفراست، ۴۲۷ لیتر، سفید / نقره ای</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/13ZvyRHCwsUzuQSj36KERxAe9m7GLSQym/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>یخچال فریزر</t>
   </si>
   <si>
     <t>یخچال فریزر کمبی اتوماتیک نقره ای دیپوینت مدل Boss Pro-S</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1LXwa1wzAJ3U7DJg0YT0hBv6nU644ACS3/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>یخچال فریزر ساید بای ساید اتوماتیک سفید دیپوینت مدل INSIDER-W</t>
   </si>
   <si>
     <t>ارتفاع 180، پهنای 92 و عمق 74 سانتی متر، میزان مصرف انرژی B، دارای 4 طبقه و 2 کشو در یخچال، ۳۹۳ لیتر، سفید / نقره ای</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1lmYyEhpoSsJhEHD7AcBBGC8smFkFYgTd/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>یخچال فریزر ساید بای ساید اتوماتیک نقره ای دیپوینت مدل INSIDER-S</t>
   </si>
   <si>
     <t>ارتفاع 180، پهنای 92 و عمق 74 سانتی متر، میزان مصرف انرژی B، دارای 4 طبقه و 2 کشو در فریزر، ۳۹۳ لیتر، سفید / نقره ای</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1Yb3C7oCWmdXx-SWHh_QB8793RtlM3TOx/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>یخچال سفید دیپوینت دوقلو مدل D5i-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی +A، دارای 5 طبقه و 3 کشو در یخچال، 330 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_iN_IpNyK_VyoVMI-_Bbw8iZPOTBNKtV/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>یخچال فریزر دوقلو</t>
   </si>
   <si>
     <t>فریزر سفید دیپوینت دوقلو مدل D5i-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی +A، دارای 1 طبقه و 7 کشو در یخچال، 277 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
     <t>یخچال نقره ای دیپوینت دوقلو مدل D5i-S</t>
   </si>
   <si>
@@ -4354,9 +4375,18 @@
     <t>یخچال سفید دیپوینت دوقلو مدل EXPLORE-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی A، دارای 4 طبقه و 2 کشو در یخچال، 454 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/154wtCv1FSUOftD13qKG51eWvR8wGRqxG/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>فریزر سفید دیپوینت دوقلو مدل EXPLORE-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی A، دارای 2 طبقه و 5 کشو در یخچال، 301 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
     <t>یخچال نقره ای دیپوینت دوقلو مدل EXPLORE-S</t>
   </si>
   <si>
@@ -4366,9 +4396,15 @@
     <t>یخچال سفید دیپوینت دوقلو مدل MAX-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی +A، دارای 3 طبقه و 2 کشو در یخچال، 350 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
     <t>فریزر سفید دیپوینت دوقلو مدل MAX-W</t>
   </si>
   <si>
+    <t>میزان مصرف انرژی +A، دارای 2 طبقه و 7 کشو در یخچال، 325 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
     <t>یخچال نقره ای دیپوینت دوقلو مدل MAX-S</t>
   </si>
   <si>
@@ -4378,7 +4414,29 @@
     <t>ماشین لباسشویی 9Kg نقره ای دیپوینت مدل WMFW0901-S Wonder</t>
   </si>
   <si>
+    <t>نوع مدل:درب از جلو 
+حداکثر ظرفیت شست و شو 9 کیلوگرم
+گزینه های سرعت چرخش:1400-1000-800-400-بدون چرخش
+تنظیمات دما:سرد-20 درجه-40 درجه-60 درجه-90 درجه سانتی گراد
+نوع قفل درب:خودکار
+صفحه نمایش:صفحه نمایش لمسی LED بزرگ
+نوع موتور:موتور بدون تسمه(DIRECT DRIVE)
+گزینه های اضافه:
+پیش شستشو-شستشو شبانه-تاخیر در شستشو-ماساژ لباس فوق العاده(super spa)-سطح آلودگی-برنامه شخصی من(my cycle)-قفل کودک-تنظیم دما-آبکشی بیشتر-سرعت</t>
+  </si>
+  <si>
     <t>ماشین لباسشویی 9Kg سفید دیپوینت مدل WMFW0901-W Wonder</t>
+  </si>
+  <si>
+    <t>نوع مدل:درب از جلو 
+حداکثر ظرفیت شست و شو 9 کیلوگرم
+گزینه های سرعت چرخش:1400-1000-800-400-بدون چرخش
+تنظیمات دما:سرد-20 درجه-40 درجه-60 درجه-90 درجه سانتی گراد
+نوع قفل درب:خودکار
+صفحه نمایش:صفحه نمایش لمسی LED بزرگ
+نوع موتور:موتور بدون تسمه(DIRECT DRIVE)
+گزینه های اضافه:
+پیش شستشو-شستشو شبانه-تاخیر در شستشو-ماساژ لباس فوق العاده(super spa)-سطح آلودگی-برنامه شخصی من(my cycle)-قفل کودک-تنظیم دما-آبکشی بیشتر-سرعت</t>
   </si>
 </sst>
 </file>
@@ -4489,25 +4547,25 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -4796,40 +4854,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C2" s="10">
         <v>1.109410629E9</v>
@@ -4857,7 +4915,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C3" s="10">
         <v>1.102420474E9</v>
@@ -4887,7 +4945,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C4" s="10">
         <v>1.108767131E9</v>
@@ -4915,7 +4973,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C5" s="10">
         <v>1.108513754E9</v>
@@ -4941,7 +4999,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C6" s="10">
         <v>1.103961018E9</v>
@@ -4971,7 +5029,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>1.109795907E9</v>
@@ -5001,7 +5059,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10">
         <v>1.107343129E9</v>
@@ -5031,7 +5089,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C9" s="10">
         <v>1.107376682E9</v>
@@ -5061,7 +5119,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10">
         <v>1.101106336E9</v>
@@ -5091,7 +5149,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C11" s="10">
         <v>1.104186523E9</v>
@@ -5119,7 +5177,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C12" s="10">
         <v>1.10473176E9</v>
@@ -5145,7 +5203,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10">
         <v>1.109650453E9</v>
@@ -5173,7 +5231,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C14" s="10">
         <v>1.10808351E9</v>
@@ -5199,7 +5257,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10">
         <v>1.109487106E9</v>
@@ -5225,7 +5283,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C16" s="10">
         <v>1.109460131E9</v>
@@ -5253,7 +5311,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C17" s="10">
         <v>1.105617587E9</v>
@@ -5279,7 +5337,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C18" s="10">
         <v>1.106819388E9</v>
@@ -5307,7 +5365,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C19" s="10">
         <v>1.001004778E9</v>
@@ -5333,7 +5391,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C20" s="10">
         <v>1.00100478E9</v>
@@ -5359,7 +5417,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C21" s="10">
         <v>1.001004782E9</v>
@@ -5385,7 +5443,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C22" s="10">
         <v>1.001004784E9</v>
@@ -5411,7 +5469,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C23" s="10">
         <v>1.104349913E9</v>
@@ -5437,7 +5495,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C24" s="10">
         <v>1.109587805E9</v>
@@ -5463,7 +5521,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C25" s="10">
         <v>1.107699532E9</v>
@@ -5489,7 +5547,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C26" s="10">
         <v>1.107648299E9</v>
@@ -5515,7 +5573,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C27" s="10">
         <v>1.109287401E9</v>
@@ -5541,7 +5599,7 @@
         <v>65</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C28" s="10">
         <v>1.001004781E9</v>
@@ -5567,7 +5625,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10">
         <v>1.001021394E9</v>
@@ -5593,7 +5651,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C30" s="10">
         <v>1.001021393E9</v>
@@ -5619,7 +5677,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C31" s="10">
         <v>1.001021391E9</v>
@@ -5645,7 +5703,7 @@
         <v>69</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C32" s="10">
         <v>1.001021395E9</v>
@@ -5671,7 +5729,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C33" s="10">
         <v>1.001021392E9</v>
@@ -5697,7 +5755,7 @@
         <v>71</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C34" s="10">
         <v>1.001006153E9</v>
@@ -5723,7 +5781,7 @@
         <v>72</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C35" s="10">
         <v>1.001010412E9</v>
@@ -5749,7 +5807,7 @@
         <v>73</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C36" s="10">
         <v>1.001006156E9</v>
@@ -5775,7 +5833,7 @@
         <v>74</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C37" s="10">
         <v>1.001006157E9</v>
@@ -5801,7 +5859,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C38" s="10">
         <v>1.001006158E9</v>
@@ -5827,7 +5885,7 @@
         <v>76</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C39" s="10">
         <v>1.001001379E9</v>
@@ -5853,7 +5911,7 @@
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C40" s="10">
         <v>1.001001377E9</v>
@@ -5879,7 +5937,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C41" s="10">
         <v>1.001005247E9</v>
@@ -5905,7 +5963,7 @@
         <v>79</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C42" s="10">
         <v>1.001001378E9</v>
@@ -5931,7 +5989,7 @@
         <v>80</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C43" s="10">
         <v>1.00100138E9</v>
@@ -5957,7 +6015,7 @@
         <v>81</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C44" s="10">
         <v>1.001005248E9</v>
@@ -5983,7 +6041,7 @@
         <v>82</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C45" s="10">
         <v>1.001001381E9</v>
@@ -6009,7 +6067,7 @@
         <v>83</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C46" s="10">
         <v>1.001005249E9</v>
@@ -6035,7 +6093,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C47" s="10">
         <v>1.101902167E9</v>
@@ -6061,7 +6119,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C48" s="10">
         <v>1.10476745E9</v>
@@ -6087,7 +6145,7 @@
         <v>86</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C49" s="10">
         <v>1.107951155E9</v>
@@ -6113,7 +6171,7 @@
         <v>87</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C50" s="10">
         <v>1.103162512E9</v>
@@ -6139,7 +6197,7 @@
         <v>88</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C51" s="10">
         <v>1.101210104E9</v>
@@ -6165,7 +6223,7 @@
         <v>89</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C52" s="10">
         <v>1.102684171E9</v>
@@ -6191,7 +6249,7 @@
         <v>90</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C53" s="10">
         <v>1.106756931E9</v>
@@ -6217,7 +6275,7 @@
         <v>91</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C54" s="10">
         <v>1.105904445E9</v>
@@ -6243,7 +6301,7 @@
         <v>92</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C55" s="10">
         <v>1.101567826E9</v>
@@ -6269,7 +6327,7 @@
         <v>93</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C56" s="10">
         <v>1.101372157E9</v>
@@ -6295,7 +6353,7 @@
         <v>94</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C57" s="10">
         <v>1.101198832E9</v>
@@ -6323,7 +6381,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C58" s="10">
         <v>1.105747685E9</v>
@@ -6351,7 +6409,7 @@
         <v>96</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C59" s="10">
         <v>1.102034608E9</v>
@@ -6379,7 +6437,7 @@
         <v>97</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C60" s="10">
         <v>1.106909378E9</v>
@@ -6407,7 +6465,7 @@
         <v>98</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C61" s="10">
         <v>1.106425921E9</v>
@@ -6435,7 +6493,7 @@
         <v>99</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C62" s="10">
         <v>1.10938833E9</v>
@@ -6463,7 +6521,7 @@
         <v>100</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C63" s="10">
         <v>1.10626332E9</v>
@@ -6491,7 +6549,7 @@
         <v>101</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C64" s="10">
         <v>1.101786232E9</v>
@@ -6519,7 +6577,7 @@
         <v>102</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C65" s="10">
         <v>1.103047943E9</v>
@@ -6547,7 +6605,7 @@
         <v>103</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C66" s="10">
         <v>1.001011708E9</v>
@@ -6573,7 +6631,7 @@
         <v>106</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C67" s="10">
         <v>1.001011816E9</v>
@@ -6599,7 +6657,7 @@
         <v>107</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C68" s="10">
         <v>1.001021157E9</v>
@@ -6627,7 +6685,7 @@
         <v>109</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C69" s="10">
         <v>1.001012566E9</v>
@@ -6655,7 +6713,7 @@
         <v>109</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C70" s="10">
         <v>1.001012092E9</v>
@@ -6683,7 +6741,7 @@
         <v>112</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C71" s="10">
         <v>1.001020005E9</v>
@@ -6711,7 +6769,7 @@
         <v>114</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C72" s="10">
         <v>1.102722242E9</v>
@@ -6737,7 +6795,7 @@
         <v>115</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C73" s="10">
         <v>1.001021166E9</v>
@@ -6765,7 +6823,7 @@
         <v>109</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C74" s="10">
         <v>1.001011734E9</v>
@@ -6793,7 +6851,7 @@
         <v>116</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C75" s="10">
         <v>1.001020003E9</v>
@@ -6821,7 +6879,7 @@
         <v>117</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C76" s="10">
         <v>1.001007259E9</v>
@@ -23523,7 +23581,7 @@
         <v>824</v>
       </c>
       <c r="B712" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C712" s="10">
         <v>1001687.0</v>
@@ -23553,7 +23611,7 @@
         <v>827</v>
       </c>
       <c r="B713" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C713" s="10">
         <v>1000343.0</v>
@@ -23583,7 +23641,7 @@
         <v>828</v>
       </c>
       <c r="B714" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C714" s="10">
         <v>1000345.0</v>
@@ -23613,7 +23671,7 @@
         <v>829</v>
       </c>
       <c r="B715" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C715" s="10">
         <v>1001634.0</v>
@@ -23639,7 +23697,7 @@
         <v>830</v>
       </c>
       <c r="B716" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C716" s="10">
         <v>1001635.0</v>
@@ -23665,7 +23723,7 @@
         <v>831</v>
       </c>
       <c r="B717" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C717" s="10">
         <v>1001636.0</v>
@@ -23691,7 +23749,7 @@
         <v>832</v>
       </c>
       <c r="B718" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C718" s="10">
         <v>1001527.0</v>
@@ -23719,7 +23777,7 @@
         <v>833</v>
       </c>
       <c r="B719" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C719" s="10">
         <v>1001526.0</v>
@@ -23747,7 +23805,7 @@
         <v>834</v>
       </c>
       <c r="B720" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C720" s="10">
         <v>1001525.0</v>
@@ -23775,7 +23833,7 @@
         <v>835</v>
       </c>
       <c r="B721" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C721" s="10">
         <v>1000222.0</v>
@@ -23801,7 +23859,7 @@
         <v>836</v>
       </c>
       <c r="B722" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C722" s="10">
         <v>1000223.0</v>
@@ -23827,7 +23885,7 @@
         <v>837</v>
       </c>
       <c r="B723" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C723" s="10">
         <v>1000224.0</v>
@@ -23853,7 +23911,7 @@
         <v>838</v>
       </c>
       <c r="B724" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C724" s="10">
         <v>1000225.0</v>
@@ -23879,7 +23937,7 @@
         <v>839</v>
       </c>
       <c r="B725" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C725" s="10">
         <v>1001237.0</v>
@@ -23905,7 +23963,7 @@
         <v>840</v>
       </c>
       <c r="B726" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C726" s="10">
         <v>1001236.0</v>
@@ -23931,7 +23989,7 @@
         <v>841</v>
       </c>
       <c r="B727" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C727" s="10">
         <v>1000227.0</v>
@@ -23957,7 +24015,7 @@
         <v>842</v>
       </c>
       <c r="B728" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C728" s="10">
         <v>1000228.0</v>
@@ -23983,7 +24041,7 @@
         <v>843</v>
       </c>
       <c r="B729" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C729" s="10">
         <v>1000229.0</v>
@@ -24009,7 +24067,7 @@
         <v>844</v>
       </c>
       <c r="B730" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C730" s="10">
         <v>1000230.0</v>
@@ -24035,7 +24093,7 @@
         <v>845</v>
       </c>
       <c r="B731" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C731" s="10">
         <v>1000341.0</v>
@@ -24065,7 +24123,7 @@
         <v>846</v>
       </c>
       <c r="B732" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C732" s="10">
         <v>1000674.0</v>
@@ -24095,7 +24153,7 @@
         <v>849</v>
       </c>
       <c r="B733" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C733" s="10">
         <v>1000374.0</v>
@@ -24123,7 +24181,7 @@
         <v>850</v>
       </c>
       <c r="B734" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C734" s="10">
         <v>1001308.0</v>
@@ -24149,7 +24207,7 @@
         <v>851</v>
       </c>
       <c r="B735" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C735" s="10">
         <v>1000242.0</v>
@@ -24177,7 +24235,7 @@
         <v>852</v>
       </c>
       <c r="B736" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C736" s="10">
         <v>1001764.0</v>
@@ -24203,7 +24261,7 @@
         <v>853</v>
       </c>
       <c r="B737" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C737" s="10">
         <v>1001766.0</v>
@@ -24229,7 +24287,7 @@
         <v>854</v>
       </c>
       <c r="B738" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C738" s="10">
         <v>1001768.0</v>
@@ -24255,7 +24313,7 @@
         <v>855</v>
       </c>
       <c r="B739" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C739" s="10">
         <v>1001674.0</v>
@@ -24283,7 +24341,7 @@
         <v>856</v>
       </c>
       <c r="B740" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C740" s="10">
         <v>1001675.0</v>
@@ -24311,7 +24369,7 @@
         <v>857</v>
       </c>
       <c r="B741" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C741" s="10">
         <v>1001677.0</v>
@@ -24339,7 +24397,7 @@
         <v>858</v>
       </c>
       <c r="B742" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C742" s="10">
         <v>1001678.0</v>
@@ -24367,7 +24425,7 @@
         <v>859</v>
       </c>
       <c r="B743" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C743" s="10">
         <v>1001676.0</v>
@@ -24395,7 +24453,7 @@
         <v>860</v>
       </c>
       <c r="B744" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C744" s="10">
         <v>1000240.0</v>
@@ -33197,7 +33255,7 @@
         <v>1261</v>
       </c>
       <c r="B1067" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C1067" s="10">
         <v>3.20127115001E11</v>
@@ -33623,7 +33681,7 @@
         <v>1277</v>
       </c>
       <c r="B1083" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C1083" s="10">
         <v>3.20127115004E11</v>
@@ -35243,17 +35301,19 @@
       <c r="F1138" s="18" t="s">
         <v>1417</v>
       </c>
-      <c r="G1138" s="12"/>
+      <c r="G1138" s="17" t="s">
+        <v>1418</v>
+      </c>
       <c r="H1138" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1138" s="18" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" s="18" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B1139" s="18" t="s">
         <v>1416</v>
@@ -35270,17 +35330,19 @@
       <c r="F1139" s="18" t="s">
         <v>1417</v>
       </c>
-      <c r="G1139" s="12"/>
+      <c r="G1139" s="17" t="s">
+        <v>1421</v>
+      </c>
       <c r="H1139" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1139" s="18" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" s="18" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B1140" s="18" t="s">
         <v>1416</v>
@@ -35295,19 +35357,21 @@
         <v>1333</v>
       </c>
       <c r="F1140" s="18" t="s">
-        <v>1421</v>
-      </c>
-      <c r="G1140" s="12"/>
+        <v>1423</v>
+      </c>
+      <c r="G1140" s="17" t="s">
+        <v>1424</v>
+      </c>
       <c r="H1140" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1140" s="18" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" s="18" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="B1141" s="18" t="s">
         <v>1416</v>
@@ -35322,19 +35386,21 @@
         <v>1333</v>
       </c>
       <c r="F1141" s="18" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G1141" s="12"/>
+        <v>1426</v>
+      </c>
+      <c r="G1141" s="17" t="s">
+        <v>1427</v>
+      </c>
       <c r="H1141" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1141" s="18" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" s="18" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="B1142" s="18" t="s">
         <v>1416</v>
@@ -35348,18 +35414,22 @@
       <c r="E1142" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1142" s="12"/>
-      <c r="G1142" s="12"/>
+      <c r="F1142" s="18" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G1142" s="17" t="s">
+        <v>1430</v>
+      </c>
       <c r="H1142" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1142" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" s="18" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="B1143" s="18" t="s">
         <v>1416</v>
@@ -35373,18 +35443,22 @@
       <c r="E1143" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1143" s="12"/>
-      <c r="G1143" s="12"/>
+      <c r="F1143" s="18" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1143" s="17" t="s">
+        <v>1430</v>
+      </c>
       <c r="H1143" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1143" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" s="18" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="B1144" s="18" t="s">
         <v>1416</v>
@@ -35398,18 +35472,22 @@
       <c r="E1144" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1144" s="12"/>
-      <c r="G1144" s="12"/>
+      <c r="F1144" s="18" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G1144" s="17" t="s">
+        <v>1430</v>
+      </c>
       <c r="H1144" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1144" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" s="18" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="B1145" s="18" t="s">
         <v>1416</v>
@@ -35423,18 +35501,22 @@
       <c r="E1145" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1145" s="12"/>
-      <c r="G1145" s="12"/>
+      <c r="F1145" s="18" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1145" s="17" t="s">
+        <v>1430</v>
+      </c>
       <c r="H1145" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1145" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" s="18" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="B1146" s="18" t="s">
         <v>1416</v>
@@ -35448,18 +35530,22 @@
       <c r="E1146" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1146" s="12"/>
-      <c r="G1146" s="12"/>
+      <c r="F1146" s="18" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G1146" s="17" t="s">
+        <v>1438</v>
+      </c>
       <c r="H1146" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1146" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" s="18" t="s">
-        <v>1430</v>
+        <v>1439</v>
       </c>
       <c r="B1147" s="18" t="s">
         <v>1416</v>
@@ -35473,18 +35559,22 @@
       <c r="E1147" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1147" s="12"/>
-      <c r="G1147" s="12"/>
+      <c r="F1147" s="18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1147" s="17" t="s">
+        <v>1438</v>
+      </c>
       <c r="H1147" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1147" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" s="18" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="B1148" s="18" t="s">
         <v>1416</v>
@@ -35498,18 +35588,22 @@
       <c r="E1148" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1148" s="12"/>
-      <c r="G1148" s="12"/>
+      <c r="F1148" s="18" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G1148" s="17" t="s">
+        <v>1438</v>
+      </c>
       <c r="H1148" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1148" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" s="18" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="B1149" s="18" t="s">
         <v>1416</v>
@@ -35523,18 +35617,22 @@
       <c r="E1149" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1149" s="12"/>
-      <c r="G1149" s="12"/>
+      <c r="F1149" s="18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1149" s="17" t="s">
+        <v>1438</v>
+      </c>
       <c r="H1149" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1149" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" s="18" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="B1150" s="18" t="s">
         <v>1416</v>
@@ -35548,18 +35646,20 @@
       <c r="E1150" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1150" s="12"/>
+      <c r="F1150" s="18" t="s">
+        <v>1444</v>
+      </c>
       <c r="G1150" s="12"/>
       <c r="H1150" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1150" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" s="18" t="s">
-        <v>1434</v>
+        <v>1445</v>
       </c>
       <c r="B1151" s="18" t="s">
         <v>1416</v>
@@ -35573,18 +35673,20 @@
       <c r="E1151" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1151" s="12"/>
+      <c r="F1151" s="18" t="s">
+        <v>1446</v>
+      </c>
       <c r="G1151" s="12"/>
       <c r="H1151" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1151" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="18" t="s">
-        <v>1435</v>
+        <v>1447</v>
       </c>
       <c r="B1152" s="18" t="s">
         <v>1416</v>
@@ -35598,18 +35700,20 @@
       <c r="E1152" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1152" s="12"/>
+      <c r="F1152" s="18" t="s">
+        <v>1444</v>
+      </c>
       <c r="G1152" s="12"/>
       <c r="H1152" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1152" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="18" t="s">
-        <v>1436</v>
+        <v>1448</v>
       </c>
       <c r="B1153" s="18" t="s">
         <v>1416</v>
@@ -35623,18 +35727,20 @@
       <c r="E1153" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1153" s="12"/>
+      <c r="F1153" s="18" t="s">
+        <v>1446</v>
+      </c>
       <c r="G1153" s="12"/>
       <c r="H1153" s="18" t="s">
         <v>1294</v>
       </c>
       <c r="I1153" s="18" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="18" t="s">
-        <v>1437</v>
+        <v>1449</v>
       </c>
       <c r="B1154" s="18" t="s">
         <v>1416</v>
@@ -35648,7 +35754,9 @@
       <c r="E1154" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1154" s="12"/>
+      <c r="F1154" s="18" t="s">
+        <v>1450</v>
+      </c>
       <c r="G1154" s="12"/>
       <c r="H1154" s="18" t="s">
         <v>1294</v>
@@ -35659,7 +35767,7 @@
     </row>
     <row r="1155">
       <c r="A1155" s="18" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="B1155" s="18" t="s">
         <v>1416</v>
@@ -35673,7 +35781,9 @@
       <c r="E1155" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="F1155" s="12"/>
+      <c r="F1155" s="18" t="s">
+        <v>1452</v>
+      </c>
       <c r="G1155" s="12"/>
       <c r="H1155" s="18" t="s">
         <v>1294</v>
@@ -39791,9 +39901,21 @@
     <hyperlink r:id="rId297" ref="G1135"/>
     <hyperlink r:id="rId298" ref="G1136"/>
     <hyperlink r:id="rId299" ref="G1137"/>
+    <hyperlink r:id="rId300" ref="G1138"/>
+    <hyperlink r:id="rId301" ref="G1139"/>
+    <hyperlink r:id="rId302" ref="G1140"/>
+    <hyperlink r:id="rId303" ref="G1141"/>
+    <hyperlink r:id="rId304" ref="G1142"/>
+    <hyperlink r:id="rId305" ref="G1143"/>
+    <hyperlink r:id="rId306" ref="G1144"/>
+    <hyperlink r:id="rId307" ref="G1145"/>
+    <hyperlink r:id="rId308" ref="G1146"/>
+    <hyperlink r:id="rId309" ref="G1147"/>
+    <hyperlink r:id="rId310" ref="G1148"/>
+    <hyperlink r:id="rId311" ref="G1149"/>
   </hyperlinks>
-  <drawing r:id="rId300"/>
-  <legacyDrawing r:id="rId301"/>
+  <drawing r:id="rId312"/>
+  <legacyDrawing r:id="rId313"/>
 </worksheet>
 </file>
 
@@ -39809,538 +39931,538 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>8</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1001687.0</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>5.1641E8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>1000341.0</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>4.52E8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>1000343.0</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>4.1697E8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>1000345.0</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>3.0962E8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>1000674.0</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>3.39E7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>1001459.0</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>2.0453E9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>1001453.0</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>1.00909E9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>1001020.0</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>1.07915E9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>1000598.0</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>1001362.0</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>6.7799E8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>1001757.0</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>1.017E8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>1001762.0</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>7.232E7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>1000501.0</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>4.238E7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>1001849.0</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>8.701E7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>1001927.0</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>8.927E8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>1001630.0</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>4.3505E8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>1001774.0</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>8.135E7</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>1001772.0</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>4.745E7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>1001770.0</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>3.615E7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>1001968.0</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>1.79669E9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>1001964.0</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <v>1.75149E9</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>1001895.0</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>1.60459E9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>1001888.0</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>1001891.0</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>1001890.0</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>1001962.0</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>1.10739E9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>1001960.0</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>1.10739E9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>1001958.0</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>1.03959E9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>1001957.0</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>1.03959E9</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>1001955.0</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="6">
         <v>1.01699E9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>1001952.0</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>9.8309E8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>1001951.0</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="6">
         <v>9.8309E8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6">
+      <c r="A34" s="5">
         <v>1001884.0</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="6">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>1001885.0</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>1001867.0</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="6">
         <v>3.2995E8</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>1001868.0</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="6">
         <v>3.2995E8</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>1001622.0</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>1.84755E9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>1001680.0</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>1.7289E9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6">
+      <c r="A40" s="5">
         <v>1001326.0</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="6">
         <v>1.5819E8</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6">
+      <c r="A41" s="5">
         <v>1001294.0</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="6">
         <v>1.5706E8</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6">
+      <c r="A42" s="5">
         <v>1001698.0</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>9.153E7</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6">
+      <c r="A43" s="5">
         <v>1001725.0</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="6">
         <v>1.2204E8</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>1001717.0</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="6">
         <v>9.379E7</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6">
+      <c r="A45" s="5">
         <v>1001822.0</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="6">
         <v>6.554E7</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6">
+      <c r="A46" s="5">
         <v>1001846.0</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="6">
         <v>4.3392E8</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6">
+      <c r="A47" s="5">
         <v>1000282.0</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="6">
         <v>2.599E7</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6">
+      <c r="A48" s="5">
         <v>1001925.0</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="6">
         <v>9.0287E8</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6">
+      <c r="A49" s="5">
         <v>1001619.0</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="6">
         <v>1.29385E9</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6">
+      <c r="A50" s="5">
         <v>1001201.0</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="6">
         <v>9.492E8</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6">
+      <c r="A51" s="5">
         <v>1001199.0</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="6">
         <v>7.0625E8</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6">
+      <c r="A52" s="5">
         <v>1.109226956E9</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="6">
         <v>7.3111E9</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6">
+      <c r="A53" s="5">
         <v>1.108040902E9</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="6">
         <v>7.0399E9</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6">
+      <c r="A54" s="5">
         <v>1.105150079E9</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="6">
         <v>7.006E9</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>1.101640902E9</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>6.8139E9</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6">
+      <c r="A56" s="5">
         <v>1.104647613E9</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>5.6952E9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6">
+      <c r="A57" s="5">
         <v>1.102837029E9</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>5.3901E9</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6">
+      <c r="A58" s="5">
         <v>1.101819678E9</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="6">
         <v>2.6668E9</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6">
+      <c r="A59" s="5">
         <v>1.108735205E9</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="6">
         <v>2.6668E9</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6">
+      <c r="A60" s="5">
         <v>1.109996356E9</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="6">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6">
+      <c r="A61" s="5">
         <v>1.10464317E9</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="6">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6">
+      <c r="A62" s="5">
         <v>1.10967804E9</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="6">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6">
+      <c r="A63" s="5">
         <v>1.103693849E9</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="6">
         <v>2.3278E9</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6">
+      <c r="A64" s="5">
         <v>1.107969437E9</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="6">
         <v>2.3052E9</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6">
+      <c r="A65" s="5">
         <v>1.103854321E9</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="6">
         <v>2.2939E9</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6">
+      <c r="A66" s="5">
         <v>1.105928955E9</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="6">
         <v>1.7176E9</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6">
+      <c r="A67" s="5">
         <v>1.104033685E9</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="6">
         <v>1.582E9</v>
       </c>
     </row>
@@ -43172,91 +43294,91 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="33.0" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="3" ht="33.0" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="33.0" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="33.0" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="33.0" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="33.0" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="33.0" customHeight="1">
-      <c r="A5" s="5" t="s">
+    <row r="8" ht="33.0" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="9" ht="33.0" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="33.0" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="10" ht="33.0" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="33.0" customHeight="1">
-      <c r="A8" s="5" t="s">
+    <row r="11" ht="33.0" customHeight="1">
+      <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" ht="33.0" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="33.0" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" ht="33.0" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/xpoint-products.xlsx
+++ b/data/xpoint-products.xlsx
@@ -61,60 +61,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6269" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6275" uniqueCount="1455">
   <si>
     <t>موضوع</t>
   </si>
   <si>
+    <t>راهنما</t>
+  </si>
+  <si>
     <t>نام محصول</t>
   </si>
   <si>
     <t>کد کالا</t>
   </si>
   <si>
-    <t>راهنما</t>
-  </si>
-  <si>
     <t>نمایش محصول</t>
   </si>
   <si>
+    <t>برند</t>
+  </si>
+  <si>
+    <t>کد محصول</t>
+  </si>
+  <si>
     <t>قیمت فروش ( ریال )</t>
   </si>
   <si>
+    <t>قیمت نقد</t>
+  </si>
+  <si>
     <t>فقط محصولی در سایت نمایش داده می‌شود که نام، برند، کد محصول و قیمت نقد داشته باشد.</t>
   </si>
   <si>
     <t>موجود کردن</t>
   </si>
   <si>
+    <t>دسته‌بندی</t>
+  </si>
+  <si>
+    <t>توضیحات</t>
+  </si>
+  <si>
     <t>قیمت نقد را وارد کنید؛ ردیف به رنگ سبز درمی‌آید و محصول در سایت موجود محسوب می‌شود.</t>
   </si>
   <si>
+    <t>عکس</t>
+  </si>
+  <si>
     <t>ناموجود کردن</t>
   </si>
   <si>
     <t>فقط قیمت نقد را خالی کنید؛ محصول از سایت حذف می‌شود ولی اطلاعات آن در شیت باقی می‌ماند.</t>
   </si>
   <si>
+    <t>دسته‌بندی اصلی</t>
+  </si>
+  <si>
+    <t>گروه اصلی</t>
+  </si>
+  <si>
     <t>فهرست برندها</t>
   </si>
   <si>
     <t>برند تمام ردیف‌های معتبر در فیلتر سایت باقی می‌ماند؛ حتی اگر قیمت محصول خالی باشد.</t>
   </si>
   <si>
-    <t>برند</t>
-  </si>
-  <si>
     <t>عکس محصول</t>
   </si>
   <si>
     <t>لینک عمومی فایل Google Drive یا شناسه فایل عکس را در ستون «عکس» قرار دهید.</t>
   </si>
   <si>
-    <t>کد محصول</t>
-  </si>
-  <si>
-    <t>توضیحات</t>
+    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
   </si>
   <si>
     <t>متن ستون «توضیحات» در پنجره جزئیات محصول نمایش داده می‌شود.</t>
@@ -123,15 +141,15 @@
     <t>آرایشی و بهداشتی</t>
   </si>
   <si>
+    <t>اپل</t>
+  </si>
+  <si>
     <t>این کالاها با دسته‌بندی «اکسسوری» ثبت شوند.</t>
   </si>
   <si>
     <t>دسته‌بندی‌های مجاز</t>
   </si>
   <si>
-    <t>قیمت نقد</t>
-  </si>
-  <si>
     <t>یخچال، ظرفشویی، لباسشویی، موبایل، لپ تاپ، اکسسوری، گجت، اسپیکر، تبلت، کنسول بازی، شارژر، تلویزیون، گجت خانگی</t>
   </si>
   <si>
@@ -144,25 +162,7 @@
     <t>پوشه بنرها</t>
   </si>
   <si>
-    <t>دسته‌بندی</t>
-  </si>
-  <si>
     <t>baner</t>
-  </si>
-  <si>
-    <t>عکس</t>
-  </si>
-  <si>
-    <t>دسته‌بندی اصلی</t>
-  </si>
-  <si>
-    <t>گروه اصلی</t>
-  </si>
-  <si>
-    <t>iPhone 17 Pro Max 512GB ZA/A Non Active Silver</t>
-  </si>
-  <si>
-    <t>اپل</t>
   </si>
   <si>
     <t>موبایل</t>
@@ -4397,6 +4397,9 @@
   </si>
   <si>
     <t>میزان مصرف انرژی +A، دارای 3 طبقه و 2 کشو در یخچال، 350 لیتر، سفید / نقره ای</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bXWG6Vxm_lAVSdr6HfVuYPhFnmvZv-Qo/view?usp=drive_link</t>
   </si>
   <si>
     <t>فریزر سفید دیپوینت دوقلو مدل MAX-W</t>
@@ -4423,6 +4426,9 @@
 نوع موتور:موتور بدون تسمه(DIRECT DRIVE)
 گزینه های اضافه:
 پیش شستشو-شستشو شبانه-تاخیر در شستشو-ماساژ لباس فوق العاده(super spa)-سطح آلودگی-برنامه شخصی من(my cycle)-قفل کودک-تنظیم دما-آبکشی بیشتر-سرعت</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FfpCn4xUJxq_79clSrLg9CYNnc8PcCSX/view?usp=drive_link</t>
   </si>
   <si>
     <t>ماشین لباسشویی 9Kg سفید دیپوینت مدل WMFW0901-W Wonder</t>
@@ -4549,6 +4555,9 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -4556,16 +4565,13 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -4854,40 +4860,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>31</v>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C2" s="10">
         <v>1.109410629E9</v>
@@ -4915,7 +4921,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="10">
         <v>1.102420474E9</v>
@@ -4945,7 +4951,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C4" s="10">
         <v>1.108767131E9</v>
@@ -4973,7 +4979,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C5" s="10">
         <v>1.108513754E9</v>
@@ -4999,7 +5005,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C6" s="10">
         <v>1.103961018E9</v>
@@ -5029,7 +5035,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C7" s="10">
         <v>1.109795907E9</v>
@@ -5059,7 +5065,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10">
         <v>1.107343129E9</v>
@@ -5089,7 +5095,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C9" s="10">
         <v>1.107376682E9</v>
@@ -5119,7 +5125,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C10" s="10">
         <v>1.101106336E9</v>
@@ -5149,7 +5155,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10">
         <v>1.104186523E9</v>
@@ -5177,7 +5183,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" s="10">
         <v>1.10473176E9</v>
@@ -5203,7 +5209,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C13" s="10">
         <v>1.109650453E9</v>
@@ -5231,7 +5237,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C14" s="10">
         <v>1.10808351E9</v>
@@ -5257,7 +5263,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C15" s="10">
         <v>1.109487106E9</v>
@@ -5283,7 +5289,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C16" s="10">
         <v>1.109460131E9</v>
@@ -5311,7 +5317,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C17" s="10">
         <v>1.105617587E9</v>
@@ -5337,7 +5343,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C18" s="10">
         <v>1.106819388E9</v>
@@ -5365,7 +5371,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C19" s="10">
         <v>1.001004778E9</v>
@@ -5391,7 +5397,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C20" s="10">
         <v>1.00100478E9</v>
@@ -5417,7 +5423,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C21" s="10">
         <v>1.001004782E9</v>
@@ -5443,7 +5449,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C22" s="10">
         <v>1.001004784E9</v>
@@ -5469,7 +5475,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C23" s="10">
         <v>1.104349913E9</v>
@@ -5495,7 +5501,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
         <v>1.109587805E9</v>
@@ -5521,7 +5527,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C25" s="10">
         <v>1.107699532E9</v>
@@ -5547,7 +5553,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C26" s="10">
         <v>1.107648299E9</v>
@@ -5573,7 +5579,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C27" s="10">
         <v>1.109287401E9</v>
@@ -5599,7 +5605,7 @@
         <v>65</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10">
         <v>1.001004781E9</v>
@@ -5625,7 +5631,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C29" s="10">
         <v>1.001021394E9</v>
@@ -5651,7 +5657,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" s="10">
         <v>1.001021393E9</v>
@@ -5677,7 +5683,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="10">
         <v>1.001021391E9</v>
@@ -5703,7 +5709,7 @@
         <v>69</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C32" s="10">
         <v>1.001021395E9</v>
@@ -5729,7 +5735,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C33" s="10">
         <v>1.001021392E9</v>
@@ -5755,7 +5761,7 @@
         <v>71</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C34" s="10">
         <v>1.001006153E9</v>
@@ -5781,7 +5787,7 @@
         <v>72</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C35" s="10">
         <v>1.001010412E9</v>
@@ -5807,7 +5813,7 @@
         <v>73</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C36" s="10">
         <v>1.001006156E9</v>
@@ -5833,7 +5839,7 @@
         <v>74</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C37" s="10">
         <v>1.001006157E9</v>
@@ -5859,7 +5865,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C38" s="10">
         <v>1.001006158E9</v>
@@ -5885,7 +5891,7 @@
         <v>76</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C39" s="10">
         <v>1.001001379E9</v>
@@ -5911,7 +5917,7 @@
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C40" s="10">
         <v>1.001001377E9</v>
@@ -5937,7 +5943,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C41" s="10">
         <v>1.001005247E9</v>
@@ -5963,7 +5969,7 @@
         <v>79</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C42" s="10">
         <v>1.001001378E9</v>
@@ -5989,7 +5995,7 @@
         <v>80</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C43" s="10">
         <v>1.00100138E9</v>
@@ -6015,7 +6021,7 @@
         <v>81</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C44" s="10">
         <v>1.001005248E9</v>
@@ -6041,7 +6047,7 @@
         <v>82</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C45" s="10">
         <v>1.001001381E9</v>
@@ -6067,7 +6073,7 @@
         <v>83</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C46" s="10">
         <v>1.001005249E9</v>
@@ -6093,7 +6099,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C47" s="10">
         <v>1.101902167E9</v>
@@ -6119,7 +6125,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C48" s="10">
         <v>1.10476745E9</v>
@@ -6145,7 +6151,7 @@
         <v>86</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C49" s="10">
         <v>1.107951155E9</v>
@@ -6171,7 +6177,7 @@
         <v>87</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C50" s="10">
         <v>1.103162512E9</v>
@@ -6197,7 +6203,7 @@
         <v>88</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C51" s="10">
         <v>1.101210104E9</v>
@@ -6223,7 +6229,7 @@
         <v>89</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C52" s="10">
         <v>1.102684171E9</v>
@@ -6249,7 +6255,7 @@
         <v>90</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C53" s="10">
         <v>1.106756931E9</v>
@@ -6275,7 +6281,7 @@
         <v>91</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C54" s="10">
         <v>1.105904445E9</v>
@@ -6301,7 +6307,7 @@
         <v>92</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C55" s="10">
         <v>1.101567826E9</v>
@@ -6327,7 +6333,7 @@
         <v>93</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C56" s="10">
         <v>1.101372157E9</v>
@@ -6353,7 +6359,7 @@
         <v>94</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C57" s="10">
         <v>1.101198832E9</v>
@@ -6381,7 +6387,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C58" s="10">
         <v>1.105747685E9</v>
@@ -6409,7 +6415,7 @@
         <v>96</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C59" s="10">
         <v>1.102034608E9</v>
@@ -6437,7 +6443,7 @@
         <v>97</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C60" s="10">
         <v>1.106909378E9</v>
@@ -6465,7 +6471,7 @@
         <v>98</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C61" s="10">
         <v>1.106425921E9</v>
@@ -6493,7 +6499,7 @@
         <v>99</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C62" s="10">
         <v>1.10938833E9</v>
@@ -6521,7 +6527,7 @@
         <v>100</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C63" s="10">
         <v>1.10626332E9</v>
@@ -6549,7 +6555,7 @@
         <v>101</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C64" s="10">
         <v>1.101786232E9</v>
@@ -6577,7 +6583,7 @@
         <v>102</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C65" s="10">
         <v>1.103047943E9</v>
@@ -6605,7 +6611,7 @@
         <v>103</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C66" s="10">
         <v>1.001011708E9</v>
@@ -6631,7 +6637,7 @@
         <v>106</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C67" s="10">
         <v>1.001011816E9</v>
@@ -6657,7 +6663,7 @@
         <v>107</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C68" s="10">
         <v>1.001021157E9</v>
@@ -6685,7 +6691,7 @@
         <v>109</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C69" s="10">
         <v>1.001012566E9</v>
@@ -6713,7 +6719,7 @@
         <v>109</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C70" s="10">
         <v>1.001012092E9</v>
@@ -6741,7 +6747,7 @@
         <v>112</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C71" s="10">
         <v>1.001020005E9</v>
@@ -6769,7 +6775,7 @@
         <v>114</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C72" s="10">
         <v>1.102722242E9</v>
@@ -6795,7 +6801,7 @@
         <v>115</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C73" s="10">
         <v>1.001021166E9</v>
@@ -6823,7 +6829,7 @@
         <v>109</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C74" s="10">
         <v>1.001011734E9</v>
@@ -6851,7 +6857,7 @@
         <v>116</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C75" s="10">
         <v>1.001020003E9</v>
@@ -6879,7 +6885,7 @@
         <v>117</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C76" s="10">
         <v>1.001007259E9</v>
@@ -23581,7 +23587,7 @@
         <v>824</v>
       </c>
       <c r="B712" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C712" s="10">
         <v>1001687.0</v>
@@ -23611,7 +23617,7 @@
         <v>827</v>
       </c>
       <c r="B713" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C713" s="10">
         <v>1000343.0</v>
@@ -23641,7 +23647,7 @@
         <v>828</v>
       </c>
       <c r="B714" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C714" s="10">
         <v>1000345.0</v>
@@ -23671,7 +23677,7 @@
         <v>829</v>
       </c>
       <c r="B715" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C715" s="10">
         <v>1001634.0</v>
@@ -23697,7 +23703,7 @@
         <v>830</v>
       </c>
       <c r="B716" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C716" s="10">
         <v>1001635.0</v>
@@ -23723,7 +23729,7 @@
         <v>831</v>
       </c>
       <c r="B717" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C717" s="10">
         <v>1001636.0</v>
@@ -23749,7 +23755,7 @@
         <v>832</v>
       </c>
       <c r="B718" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C718" s="10">
         <v>1001527.0</v>
@@ -23777,7 +23783,7 @@
         <v>833</v>
       </c>
       <c r="B719" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C719" s="10">
         <v>1001526.0</v>
@@ -23805,7 +23811,7 @@
         <v>834</v>
       </c>
       <c r="B720" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C720" s="10">
         <v>1001525.0</v>
@@ -23833,7 +23839,7 @@
         <v>835</v>
       </c>
       <c r="B721" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C721" s="10">
         <v>1000222.0</v>
@@ -23859,7 +23865,7 @@
         <v>836</v>
       </c>
       <c r="B722" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C722" s="10">
         <v>1000223.0</v>
@@ -23885,7 +23891,7 @@
         <v>837</v>
       </c>
       <c r="B723" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C723" s="10">
         <v>1000224.0</v>
@@ -23911,7 +23917,7 @@
         <v>838</v>
       </c>
       <c r="B724" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C724" s="10">
         <v>1000225.0</v>
@@ -23937,7 +23943,7 @@
         <v>839</v>
       </c>
       <c r="B725" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C725" s="10">
         <v>1001237.0</v>
@@ -23963,7 +23969,7 @@
         <v>840</v>
       </c>
       <c r="B726" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C726" s="10">
         <v>1001236.0</v>
@@ -23989,7 +23995,7 @@
         <v>841</v>
       </c>
       <c r="B727" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C727" s="10">
         <v>1000227.0</v>
@@ -24015,7 +24021,7 @@
         <v>842</v>
       </c>
       <c r="B728" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C728" s="10">
         <v>1000228.0</v>
@@ -24041,7 +24047,7 @@
         <v>843</v>
       </c>
       <c r="B729" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C729" s="10">
         <v>1000229.0</v>
@@ -24067,7 +24073,7 @@
         <v>844</v>
       </c>
       <c r="B730" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C730" s="10">
         <v>1000230.0</v>
@@ -24093,7 +24099,7 @@
         <v>845</v>
       </c>
       <c r="B731" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C731" s="10">
         <v>1000341.0</v>
@@ -24123,7 +24129,7 @@
         <v>846</v>
       </c>
       <c r="B732" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C732" s="10">
         <v>1000674.0</v>
@@ -24153,7 +24159,7 @@
         <v>849</v>
       </c>
       <c r="B733" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C733" s="10">
         <v>1000374.0</v>
@@ -24181,7 +24187,7 @@
         <v>850</v>
       </c>
       <c r="B734" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C734" s="10">
         <v>1001308.0</v>
@@ -24207,7 +24213,7 @@
         <v>851</v>
       </c>
       <c r="B735" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C735" s="10">
         <v>1000242.0</v>
@@ -24235,7 +24241,7 @@
         <v>852</v>
       </c>
       <c r="B736" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C736" s="10">
         <v>1001764.0</v>
@@ -24261,7 +24267,7 @@
         <v>853</v>
       </c>
       <c r="B737" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C737" s="10">
         <v>1001766.0</v>
@@ -24287,7 +24293,7 @@
         <v>854</v>
       </c>
       <c r="B738" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C738" s="10">
         <v>1001768.0</v>
@@ -24313,7 +24319,7 @@
         <v>855</v>
       </c>
       <c r="B739" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C739" s="10">
         <v>1001674.0</v>
@@ -24341,7 +24347,7 @@
         <v>856</v>
       </c>
       <c r="B740" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C740" s="10">
         <v>1001675.0</v>
@@ -24369,7 +24375,7 @@
         <v>857</v>
       </c>
       <c r="B741" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C741" s="10">
         <v>1001677.0</v>
@@ -24397,7 +24403,7 @@
         <v>858</v>
       </c>
       <c r="B742" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C742" s="10">
         <v>1001678.0</v>
@@ -24425,7 +24431,7 @@
         <v>859</v>
       </c>
       <c r="B743" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C743" s="10">
         <v>1001676.0</v>
@@ -24453,7 +24459,7 @@
         <v>860</v>
       </c>
       <c r="B744" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C744" s="10">
         <v>1000240.0</v>
@@ -33255,7 +33261,7 @@
         <v>1261</v>
       </c>
       <c r="B1067" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C1067" s="10">
         <v>3.20127115001E11</v>
@@ -33681,7 +33687,7 @@
         <v>1277</v>
       </c>
       <c r="B1083" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C1083" s="10">
         <v>3.20127115004E11</v>
@@ -35649,7 +35655,9 @@
       <c r="F1150" s="18" t="s">
         <v>1444</v>
       </c>
-      <c r="G1150" s="12"/>
+      <c r="G1150" s="17" t="s">
+        <v>1445</v>
+      </c>
       <c r="H1150" s="18" t="s">
         <v>1294</v>
       </c>
@@ -35659,7 +35667,7 @@
     </row>
     <row r="1151">
       <c r="A1151" s="18" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1151" s="18" t="s">
         <v>1416</v>
@@ -35674,9 +35682,11 @@
         <v>1333</v>
       </c>
       <c r="F1151" s="18" t="s">
-        <v>1446</v>
-      </c>
-      <c r="G1151" s="12"/>
+        <v>1447</v>
+      </c>
+      <c r="G1151" s="17" t="s">
+        <v>1445</v>
+      </c>
       <c r="H1151" s="18" t="s">
         <v>1294</v>
       </c>
@@ -35686,7 +35696,7 @@
     </row>
     <row r="1152">
       <c r="A1152" s="18" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B1152" s="18" t="s">
         <v>1416</v>
@@ -35703,7 +35713,9 @@
       <c r="F1152" s="18" t="s">
         <v>1444</v>
       </c>
-      <c r="G1152" s="12"/>
+      <c r="G1152" s="17" t="s">
+        <v>1445</v>
+      </c>
       <c r="H1152" s="18" t="s">
         <v>1294</v>
       </c>
@@ -35713,7 +35725,7 @@
     </row>
     <row r="1153">
       <c r="A1153" s="18" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B1153" s="18" t="s">
         <v>1416</v>
@@ -35728,9 +35740,11 @@
         <v>1333</v>
       </c>
       <c r="F1153" s="18" t="s">
-        <v>1446</v>
-      </c>
-      <c r="G1153" s="12"/>
+        <v>1447</v>
+      </c>
+      <c r="G1153" s="17" t="s">
+        <v>1445</v>
+      </c>
       <c r="H1153" s="18" t="s">
         <v>1294</v>
       </c>
@@ -35740,7 +35754,7 @@
     </row>
     <row r="1154">
       <c r="A1154" s="18" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1154" s="18" t="s">
         <v>1416</v>
@@ -35755,9 +35769,11 @@
         <v>1333</v>
       </c>
       <c r="F1154" s="18" t="s">
-        <v>1450</v>
-      </c>
-      <c r="G1154" s="12"/>
+        <v>1451</v>
+      </c>
+      <c r="G1154" s="17" t="s">
+        <v>1452</v>
+      </c>
       <c r="H1154" s="18" t="s">
         <v>1294</v>
       </c>
@@ -35767,7 +35783,7 @@
     </row>
     <row r="1155">
       <c r="A1155" s="18" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B1155" s="18" t="s">
         <v>1416</v>
@@ -35782,9 +35798,11 @@
         <v>1333</v>
       </c>
       <c r="F1155" s="18" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G1155" s="17" t="s">
         <v>1452</v>
       </c>
-      <c r="G1155" s="12"/>
       <c r="H1155" s="18" t="s">
         <v>1294</v>
       </c>
@@ -39913,9 +39931,15 @@
     <hyperlink r:id="rId309" ref="G1147"/>
     <hyperlink r:id="rId310" ref="G1148"/>
     <hyperlink r:id="rId311" ref="G1149"/>
+    <hyperlink r:id="rId312" ref="G1150"/>
+    <hyperlink r:id="rId313" ref="G1151"/>
+    <hyperlink r:id="rId314" ref="G1152"/>
+    <hyperlink r:id="rId315" ref="G1153"/>
+    <hyperlink r:id="rId316" ref="G1154"/>
+    <hyperlink r:id="rId317" ref="G1155"/>
   </hyperlinks>
-  <drawing r:id="rId312"/>
-  <legacyDrawing r:id="rId313"/>
+  <drawing r:id="rId318"/>
+  <legacyDrawing r:id="rId319"/>
 </worksheet>
 </file>
 
@@ -39931,538 +39955,538 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1001687.0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>5.1641E8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>1000341.0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>4.52E8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1000343.0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>4.1697E8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1000345.0</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>3.0962E8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>1000674.0</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>3.39E7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>1001459.0</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>2.0453E9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>1001453.0</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>1.00909E9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>1001020.0</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>1.07915E9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>1000598.0</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>1001362.0</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>6.7799E8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>1001757.0</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>1.017E8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>1001762.0</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>7.232E7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>1000501.0</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>4.238E7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>1001849.0</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>8.701E7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>1001927.0</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>8.927E8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>1001630.0</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>4.3505E8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>1001774.0</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>8.135E7</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>1001772.0</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>4.745E7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>1001770.0</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>3.615E7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>1001968.0</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>1.79669E9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>1001964.0</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>1.75149E9</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>1001895.0</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>1.60459E9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>1001888.0</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>1001891.0</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>1001890.0</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>1.28254E9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>1001962.0</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>1.10739E9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5">
+      <c r="A28" s="6">
         <v>1001960.0</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="7">
         <v>1.10739E9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5">
+      <c r="A29" s="6">
         <v>1001958.0</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="7">
         <v>1.03959E9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="6">
         <v>1001957.0</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="7">
         <v>1.03959E9</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="6">
         <v>1001955.0</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="7">
         <v>1.01699E9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5">
+      <c r="A32" s="6">
         <v>1001952.0</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="7">
         <v>9.8309E8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>1001951.0</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="7">
         <v>9.8309E8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>1001884.0</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="7">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>1001885.0</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="7">
         <v>8.2489E8</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>1001867.0</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="7">
         <v>3.2995E8</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>1001868.0</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="7">
         <v>3.2995E8</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>1001622.0</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="7">
         <v>1.84755E9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>1001680.0</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="7">
         <v>1.7289E9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>1001326.0</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="7">
         <v>1.5819E8</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>1001294.0</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="7">
         <v>1.5706E8</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>1001698.0</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="7">
         <v>9.153E7</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>1001725.0</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="7">
         <v>1.2204E8</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>1001717.0</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="7">
         <v>9.379E7</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>1001822.0</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="7">
         <v>6.554E7</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>1001846.0</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="7">
         <v>4.3392E8</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>1000282.0</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="7">
         <v>2.599E7</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5">
+      <c r="A48" s="6">
         <v>1001925.0</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="7">
         <v>9.0287E8</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5">
+      <c r="A49" s="6">
         <v>1001619.0</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="7">
         <v>1.29385E9</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5">
+      <c r="A50" s="6">
         <v>1001201.0</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="7">
         <v>9.492E8</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5">
+      <c r="A51" s="6">
         <v>1001199.0</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="7">
         <v>7.0625E8</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5">
+      <c r="A52" s="6">
         <v>1.109226956E9</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="7">
         <v>7.3111E9</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5">
+      <c r="A53" s="6">
         <v>1.108040902E9</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="7">
         <v>7.0399E9</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5">
+      <c r="A54" s="6">
         <v>1.105150079E9</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="7">
         <v>7.006E9</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5">
+      <c r="A55" s="6">
         <v>1.101640902E9</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="7">
         <v>6.8139E9</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5">
+      <c r="A56" s="6">
         <v>1.104647613E9</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="7">
         <v>5.6952E9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5">
+      <c r="A57" s="6">
         <v>1.102837029E9</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="7">
         <v>5.3901E9</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5">
+      <c r="A58" s="6">
         <v>1.101819678E9</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="7">
         <v>2.6668E9</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5">
+      <c r="A59" s="6">
         <v>1.108735205E9</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="7">
         <v>2.6668E9</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5">
+      <c r="A60" s="6">
         <v>1.109996356E9</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="7">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5">
+      <c r="A61" s="6">
         <v>1.10464317E9</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="7">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5">
+      <c r="A62" s="6">
         <v>1.10967804E9</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="7">
         <v>2.3617E9</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5">
+      <c r="A63" s="6">
         <v>1.103693849E9</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="7">
         <v>2.3278E9</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5">
+      <c r="A64" s="6">
         <v>1.107969437E9</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="7">
         <v>2.3052E9</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5">
+      <c r="A65" s="6">
         <v>1.103854321E9</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="7">
         <v>2.2939E9</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5">
+      <c r="A66" s="6">
         <v>1.105928955E9</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="7">
         <v>1.7176E9</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5">
+      <c r="A67" s="6">
         <v>1.104033685E9</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="7">
         <v>1.582E9</v>
       </c>
     </row>
@@ -43298,87 +43322,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="33.0" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="33.0" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="33.0" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="33.0" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="33.0" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>25</v>
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
+      <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
